--- a/docs/dataset/CAMRI_ARG_Test_Dataset.xlsx
+++ b/docs/dataset/CAMRI_ARG_Test_Dataset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ARG Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARG Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,6 +529,16 @@
           <t>copies/mL</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>copies/mL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -563,42 +573,52 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>blaKPC</t>
+          <t>AY456_qepA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>blaCTX_M</t>
+          <t>AY461_qnrS2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>vanA</t>
+          <t>AY466_MCR-1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>blaNDM</t>
+          <t>AY134_blaCTX-M_5</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>blaSHV</t>
+          <t>AY152_blaNDM</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>tetO</t>
+          <t>AY104_blaSHV_1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>tetM</t>
+          <t>AY601_blaOXA48</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>qnrA</t>
+          <t>AY153_blaKPC_2</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AY8_AAC6-Ib_1</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>AY32_floR_1</t>
         </is>
       </c>
     </row>
@@ -634,28 +654,34 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>639426.8</v>
       </c>
       <c r="H3" t="n">
-        <v>147582.6</v>
+        <v>762510.8</v>
       </c>
       <c r="I3" t="n">
-        <v>96661.3</v>
+        <v>419224.9</v>
       </c>
       <c r="J3" t="n">
-        <v>319399</v>
+        <v>728545.1</v>
       </c>
       <c r="K3" t="n">
-        <v>213908.9</v>
+        <v>380381</v>
       </c>
       <c r="L3" t="n">
-        <v>200476.5</v>
+        <v>85613</v>
       </c>
       <c r="M3" t="n">
-        <v>490844.4</v>
+        <v>91326.89999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>467919.1</v>
+        <v>338561.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>672340.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>451554.9</v>
       </c>
     </row>
     <row r="4">
@@ -690,28 +716,34 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>25010.8</v>
       </c>
       <c r="H4" t="n">
-        <v>134048.3</v>
+        <v>539379</v>
       </c>
       <c r="I4" t="n">
-        <v>98921.10000000001</v>
+        <v>583672.3</v>
       </c>
       <c r="J4" t="n">
-        <v>171884.6</v>
+        <v>313677.3</v>
       </c>
       <c r="K4" t="n">
-        <v>107897.6</v>
+        <v>5896.1</v>
       </c>
       <c r="L4" t="n">
-        <v>200352.4</v>
+        <v>720074.7</v>
       </c>
       <c r="M4" t="n">
-        <v>47957.1</v>
+        <v>961911.1</v>
       </c>
       <c r="N4" t="n">
-        <v>276935.6</v>
+        <v>692704.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>584560.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>228493.6</v>
       </c>
     </row>
     <row r="5">
@@ -746,28 +778,34 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>153986.6</v>
+        <v>275029.3</v>
       </c>
       <c r="H5" t="n">
-        <v>127771.2</v>
+        <v>778626.5</v>
       </c>
       <c r="I5" t="n">
-        <v>73559.39999999999</v>
+        <v>522782.7</v>
       </c>
       <c r="J5" t="n">
-        <v>191475.5</v>
+        <v>606208.9</v>
       </c>
       <c r="K5" t="n">
-        <v>91039.3</v>
+        <v>351758.8</v>
       </c>
       <c r="L5" t="n">
-        <v>74775.10000000001</v>
+        <v>488577.8</v>
       </c>
       <c r="M5" t="n">
-        <v>182566.4</v>
+        <v>835958.6</v>
       </c>
       <c r="N5" t="n">
-        <v>160414.8</v>
+        <v>649836.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>822417.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>338931.6</v>
       </c>
     </row>
     <row r="6">
@@ -802,28 +840,34 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>380953.6</v>
+        <v>223210.7</v>
       </c>
       <c r="H6" t="n">
-        <v>297947.7</v>
+        <v>530353.7</v>
       </c>
       <c r="I6" t="n">
-        <v>262800.8</v>
+        <v>934706.3</v>
       </c>
       <c r="J6" t="n">
-        <v>180956.3</v>
+        <v>511423.1</v>
       </c>
       <c r="K6" t="n">
-        <v>56193.2</v>
+        <v>753475.1</v>
       </c>
       <c r="L6" t="n">
-        <v>451453.8</v>
+        <v>758164.7</v>
       </c>
       <c r="M6" t="n">
-        <v>268376.4</v>
+        <v>575199.1</v>
       </c>
       <c r="N6" t="n">
-        <v>427257.6</v>
+        <v>851765.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>940291.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>453498.9</v>
       </c>
     </row>
     <row r="7">
@@ -858,28 +902,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>136084.6</v>
+        <v>736471.2</v>
       </c>
       <c r="H7" t="n">
-        <v>97806.5</v>
+        <v>571.9</v>
       </c>
       <c r="I7" t="n">
-        <v>89140.89999999999</v>
+        <v>204259.2</v>
       </c>
       <c r="J7" t="n">
-        <v>26458.3</v>
+        <v>385195.4</v>
       </c>
       <c r="K7" t="n">
-        <v>112817.1</v>
+        <v>853448</v>
       </c>
       <c r="L7" t="n">
-        <v>134579.7</v>
+        <v>690609.3</v>
       </c>
       <c r="M7" t="n">
-        <v>4432.3</v>
+        <v>950786.3</v>
       </c>
       <c r="N7" t="n">
-        <v>682.9</v>
+        <v>852341.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>108346.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>415989.7</v>
       </c>
     </row>
     <row r="8">
@@ -914,28 +964,34 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3660.7</v>
+        <v>676699.5</v>
       </c>
       <c r="H8" t="n">
-        <v>35022.2</v>
+        <v>324156.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3022.2</v>
+        <v>716191.8</v>
       </c>
       <c r="J8" t="n">
-        <v>49307</v>
+        <v>576588</v>
       </c>
       <c r="K8" t="n">
-        <v>14361.7</v>
+        <v>953430.3</v>
       </c>
       <c r="L8" t="n">
-        <v>6780.1</v>
+        <v>645902.9</v>
       </c>
       <c r="M8" t="n">
-        <v>36467.2</v>
+        <v>999572.4</v>
       </c>
       <c r="N8" t="n">
-        <v>18729.3</v>
+        <v>859342.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>233821.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>95085.8</v>
       </c>
     </row>
     <row r="9">
@@ -970,28 +1026,34 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>134588.7</v>
+        <v>892179.6</v>
       </c>
       <c r="H9" t="n">
-        <v>113280</v>
+        <v>19476.7</v>
       </c>
       <c r="I9" t="n">
-        <v>289245.1</v>
+        <v>238686</v>
       </c>
       <c r="J9" t="n">
-        <v>39940.3</v>
+        <v>254722.5</v>
       </c>
       <c r="K9" t="n">
-        <v>35634</v>
+        <v>419021.3</v>
       </c>
       <c r="L9" t="n">
-        <v>117947.9</v>
+        <v>490821.3</v>
       </c>
       <c r="M9" t="n">
-        <v>293618.4</v>
+        <v>672281.6</v>
       </c>
       <c r="N9" t="n">
-        <v>226866</v>
+        <v>380009.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25024.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>426764</v>
       </c>
     </row>
     <row r="10">
@@ -1026,28 +1088,34 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>463272.4</v>
+        <v>86938.8</v>
       </c>
       <c r="H10" t="n">
-        <v>424416</v>
+        <v>929098.6</v>
       </c>
       <c r="I10" t="n">
-        <v>230049.2</v>
+        <v>395785.8</v>
       </c>
       <c r="J10" t="n">
-        <v>155543.8</v>
+        <v>708785.3</v>
       </c>
       <c r="K10" t="n">
-        <v>875270.6</v>
+        <v>747515.7</v>
       </c>
       <c r="L10" t="n">
-        <v>32701.2</v>
+        <v>792932.9</v>
       </c>
       <c r="M10" t="n">
-        <v>615115.7</v>
+        <v>269511</v>
       </c>
       <c r="N10" t="n">
-        <v>889096.8</v>
+        <v>316661.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>884234.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>665107.9</v>
       </c>
     </row>
     <row r="11">
@@ -1082,28 +1150,34 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>33738.7</v>
+        <v>421921.8</v>
       </c>
       <c r="H11" t="n">
-        <v>223275.9</v>
+        <v>878721.9</v>
       </c>
       <c r="I11" t="n">
-        <v>436119</v>
+        <v>671690.2</v>
       </c>
       <c r="J11" t="n">
-        <v>22213.9</v>
+        <v>1691.3</v>
       </c>
       <c r="K11" t="n">
-        <v>269925.9</v>
+        <v>546132.3</v>
       </c>
       <c r="L11" t="n">
-        <v>388054.2</v>
+        <v>93053.39999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>496742.4</v>
+        <v>40231.7</v>
       </c>
       <c r="N11" t="n">
-        <v>458206.9</v>
+        <v>718717.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>561407.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>374301</v>
       </c>
     </row>
     <row r="12">
@@ -1138,28 +1212,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>577686.1</v>
+        <v>29797.2</v>
       </c>
       <c r="H12" t="n">
-        <v>818473.3</v>
+        <v>831665.5</v>
       </c>
       <c r="I12" t="n">
-        <v>876320.2</v>
+        <v>299997.1</v>
       </c>
       <c r="J12" t="n">
-        <v>521490.4</v>
+        <v>925575.2</v>
       </c>
       <c r="K12" t="n">
-        <v>275516.3</v>
+        <v>603252.6</v>
       </c>
       <c r="L12" t="n">
-        <v>591871.3</v>
+        <v>221596.4</v>
       </c>
       <c r="M12" t="n">
-        <v>175545.6</v>
+        <v>756268.8</v>
       </c>
       <c r="N12" t="n">
-        <v>556072.7</v>
+        <v>759401.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>915255.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>152638.9</v>
       </c>
     </row>
     <row r="13">
@@ -1194,28 +1274,34 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>17227.3</v>
+        <v>218638</v>
       </c>
       <c r="H13" t="n">
-        <v>19063.9</v>
+        <v>307514.1</v>
       </c>
       <c r="I13" t="n">
-        <v>34818.5</v>
+        <v>316177.2</v>
       </c>
       <c r="J13" t="n">
-        <v>15001.4</v>
+        <v>538452</v>
       </c>
       <c r="K13" t="n">
-        <v>26901</v>
+        <v>220538.7</v>
       </c>
       <c r="L13" t="n">
-        <v>11275</v>
+        <v>691787.2</v>
       </c>
       <c r="M13" t="n">
-        <v>7226.1</v>
+        <v>470500.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2890.6</v>
+        <v>872383</v>
+      </c>
+      <c r="O13" t="n">
+        <v>221367.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>922985</v>
       </c>
     </row>
     <row r="14">
@@ -1250,28 +1336,34 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>208312.3</v>
+        <v>505355.3</v>
       </c>
       <c r="H14" t="n">
-        <v>194270.7</v>
+        <v>57925.2</v>
       </c>
       <c r="I14" t="n">
-        <v>165198.5</v>
+        <v>751864.5</v>
       </c>
       <c r="J14" t="n">
-        <v>224948.4</v>
+        <v>719430</v>
       </c>
       <c r="K14" t="n">
-        <v>267864.2</v>
+        <v>219421.6</v>
       </c>
       <c r="L14" t="n">
-        <v>25863.2</v>
+        <v>306206</v>
       </c>
       <c r="M14" t="n">
-        <v>302524.2</v>
+        <v>651509.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>35899.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>63217</v>
+      </c>
+      <c r="P14" t="n">
+        <v>67133.3</v>
       </c>
     </row>
     <row r="15">
@@ -1306,28 +1398,34 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>160945.8</v>
+        <v>26536</v>
       </c>
       <c r="H15" t="n">
-        <v>134316.4</v>
+        <v>878009.6</v>
       </c>
       <c r="I15" t="n">
-        <v>41841.1</v>
+        <v>72543.10000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>60693.4</v>
+        <v>741950.1</v>
       </c>
       <c r="K15" t="n">
-        <v>42424.6</v>
+        <v>435836</v>
       </c>
       <c r="L15" t="n">
-        <v>148315.7</v>
+        <v>581555.6</v>
       </c>
       <c r="M15" t="n">
-        <v>150885.8</v>
+        <v>916072.8</v>
       </c>
       <c r="N15" t="n">
-        <v>139149.6</v>
+        <v>68420.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>823855.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>831771.9</v>
       </c>
     </row>
     <row r="16">
@@ -1362,28 +1460,34 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>119019.8</v>
+        <v>198837.7</v>
       </c>
       <c r="H16" t="n">
-        <v>96518.39999999999</v>
+        <v>946949.4</v>
       </c>
       <c r="I16" t="n">
-        <v>139901.8</v>
+        <v>458285.5</v>
       </c>
       <c r="J16" t="n">
-        <v>92561.3</v>
+        <v>670628.5</v>
       </c>
       <c r="K16" t="n">
-        <v>264849.4</v>
+        <v>29024.8</v>
       </c>
       <c r="L16" t="n">
-        <v>240854.8</v>
+        <v>473260.5</v>
       </c>
       <c r="M16" t="n">
-        <v>228500.6</v>
+        <v>181489.1</v>
       </c>
       <c r="N16" t="n">
-        <v>60978.1</v>
+        <v>631161</v>
+      </c>
+      <c r="O16" t="n">
+        <v>909387.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>93230.10000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1418,28 +1522,34 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22953.2</v>
+        <v>649884.4</v>
       </c>
       <c r="H17" t="n">
-        <v>370652.1</v>
+        <v>85653.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>998454.4</v>
       </c>
       <c r="J17" t="n">
-        <v>292057.5</v>
+        <v>364221.5</v>
       </c>
       <c r="K17" t="n">
-        <v>147666.6</v>
+        <v>336129.5</v>
       </c>
       <c r="L17" t="n">
-        <v>115086.3</v>
+        <v>530921.9</v>
       </c>
       <c r="M17" t="n">
-        <v>122940.4</v>
+        <v>585329.6</v>
       </c>
       <c r="N17" t="n">
-        <v>471737.9</v>
+        <v>920929.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>302190.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>96564.39999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1474,28 +1584,34 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>763478.9</v>
+        <v>544941.5</v>
       </c>
       <c r="H18" t="n">
-        <v>723696.2</v>
+        <v>485990.5</v>
       </c>
       <c r="I18" t="n">
-        <v>461098.6</v>
+        <v>996096.4</v>
       </c>
       <c r="J18" t="n">
-        <v>352500.1</v>
+        <v>69973.8</v>
       </c>
       <c r="K18" t="n">
-        <v>546773.1</v>
+        <v>679141.9</v>
       </c>
       <c r="L18" t="n">
-        <v>889419.8</v>
+        <v>425503.8</v>
       </c>
       <c r="M18" t="n">
-        <v>957258.3</v>
+        <v>634784.7</v>
       </c>
       <c r="N18" t="n">
-        <v>839149</v>
+        <v>997425.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>408295.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>738796</v>
       </c>
     </row>
     <row r="19">
@@ -1530,28 +1646,34 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>245407.9</v>
+        <v>220440.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1964.8</v>
+        <v>69212.5</v>
       </c>
       <c r="I19" t="n">
-        <v>189229</v>
+        <v>73260.7</v>
       </c>
       <c r="J19" t="n">
-        <v>45351.3</v>
+        <v>664237.7</v>
       </c>
       <c r="K19" t="n">
-        <v>136830.1</v>
+        <v>404316.7</v>
       </c>
       <c r="L19" t="n">
-        <v>191336.7</v>
+        <v>745935.4</v>
       </c>
       <c r="M19" t="n">
-        <v>273829.8</v>
+        <v>491725.8</v>
       </c>
       <c r="N19" t="n">
-        <v>4768.7</v>
+        <v>746766.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>139777</v>
+      </c>
+      <c r="P19" t="n">
+        <v>811769.3</v>
       </c>
     </row>
     <row r="20">
@@ -1586,28 +1708,34 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>82314.8</v>
+        <v>589265.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>760602.2</v>
       </c>
       <c r="I20" t="n">
-        <v>107184.8</v>
+        <v>213154.3</v>
       </c>
       <c r="J20" t="n">
-        <v>100483</v>
+        <v>330200</v>
       </c>
       <c r="K20" t="n">
-        <v>86160.2</v>
+        <v>165044.7</v>
       </c>
       <c r="L20" t="n">
-        <v>35919</v>
+        <v>330791.3</v>
       </c>
       <c r="M20" t="n">
-        <v>104915.1</v>
+        <v>91242.39999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>123986.6</v>
+        <v>433971.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>946261.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>556370.7</v>
       </c>
     </row>
     <row r="21">
@@ -1642,28 +1770,34 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>17728.5</v>
+        <v>809430.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3960.2</v>
+        <v>765834.4</v>
       </c>
       <c r="I21" t="n">
-        <v>22955.3</v>
+        <v>265200.4</v>
       </c>
       <c r="J21" t="n">
-        <v>34864.8</v>
+        <v>313915.6</v>
       </c>
       <c r="K21" t="n">
-        <v>41404.8</v>
+        <v>467390.1</v>
       </c>
       <c r="L21" t="n">
-        <v>49583.8</v>
+        <v>702854.9</v>
       </c>
       <c r="M21" t="n">
-        <v>1593.9</v>
+        <v>347961.1</v>
       </c>
       <c r="N21" t="n">
-        <v>18864.7</v>
+        <v>98443.10000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>304364.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>586465.1</v>
       </c>
     </row>
     <row r="22">
@@ -1698,28 +1832,34 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>636929.7</v>
+        <v>6498.8</v>
       </c>
       <c r="H22" t="n">
-        <v>83144.8</v>
+        <v>128391.5</v>
       </c>
       <c r="I22" t="n">
-        <v>645084.8</v>
+        <v>933259.4</v>
       </c>
       <c r="J22" t="n">
-        <v>977340.6</v>
+        <v>848015.3</v>
       </c>
       <c r="K22" t="n">
-        <v>894843.8</v>
+        <v>127627.8</v>
       </c>
       <c r="L22" t="n">
-        <v>230151.6</v>
+        <v>270916.4</v>
       </c>
       <c r="M22" t="n">
-        <v>692441.6</v>
+        <v>333308.4</v>
       </c>
       <c r="N22" t="n">
-        <v>271459.5</v>
+        <v>633747.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>492624.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>561586.4</v>
       </c>
     </row>
     <row r="23">
@@ -1754,28 +1894,34 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>684586.5</v>
+        <v>805819.3</v>
       </c>
       <c r="H23" t="n">
-        <v>543259.2</v>
+        <v>475282.4</v>
       </c>
       <c r="I23" t="n">
-        <v>179764.8</v>
+        <v>880864.2</v>
       </c>
       <c r="J23" t="n">
-        <v>16150.3</v>
+        <v>719754.3</v>
       </c>
       <c r="K23" t="n">
-        <v>144619.5</v>
+        <v>622257</v>
       </c>
       <c r="L23" t="n">
-        <v>820991.9</v>
+        <v>251403.7</v>
       </c>
       <c r="M23" t="n">
-        <v>299627.3</v>
+        <v>670133.5</v>
       </c>
       <c r="N23" t="n">
-        <v>566912.6</v>
+        <v>872579.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>97192</v>
+      </c>
+      <c r="P23" t="n">
+        <v>329646</v>
       </c>
     </row>
     <row r="24">
@@ -1810,28 +1956,34 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>203126.6</v>
+        <v>698139.4</v>
       </c>
       <c r="H24" t="n">
-        <v>115184.7</v>
+        <v>549803.6</v>
       </c>
       <c r="I24" t="n">
-        <v>237159.9</v>
+        <v>879270.2</v>
       </c>
       <c r="J24" t="n">
-        <v>23574.4</v>
+        <v>300322.3</v>
       </c>
       <c r="K24" t="n">
-        <v>103790.6</v>
+        <v>26966.5</v>
       </c>
       <c r="L24" t="n">
-        <v>69681.60000000001</v>
+        <v>120655.9</v>
       </c>
       <c r="M24" t="n">
-        <v>181570.4</v>
+        <v>857733.1</v>
       </c>
       <c r="N24" t="n">
-        <v>178702.8</v>
+        <v>443678.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>887259.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>122231.3</v>
       </c>
     </row>
     <row r="25">
@@ -1866,28 +2018,34 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>16325.6</v>
+        <v>340250.5</v>
       </c>
       <c r="H25" t="n">
-        <v>39179.6</v>
+        <v>265056.6</v>
       </c>
       <c r="I25" t="n">
-        <v>11414.6</v>
+        <v>369527.1</v>
       </c>
       <c r="J25" t="n">
-        <v>18777.6</v>
+        <v>309284.7</v>
       </c>
       <c r="K25" t="n">
-        <v>29297.9</v>
+        <v>394020.3</v>
       </c>
       <c r="L25" t="n">
-        <v>38610.6</v>
+        <v>192584.3</v>
       </c>
       <c r="M25" t="n">
-        <v>12330</v>
+        <v>329803.7</v>
       </c>
       <c r="N25" t="n">
-        <v>13405.9</v>
+        <v>694001.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>135664</v>
+      </c>
+      <c r="P25" t="n">
+        <v>353598.1</v>
       </c>
     </row>
     <row r="26">
@@ -1922,28 +2080,34 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>783998.3</v>
+        <v>155479.5</v>
       </c>
       <c r="H26" t="n">
-        <v>389927.2</v>
+        <v>872433</v>
       </c>
       <c r="I26" t="n">
-        <v>91974.7</v>
+        <v>157746.8</v>
       </c>
       <c r="J26" t="n">
-        <v>445013.5</v>
+        <v>408392.9</v>
       </c>
       <c r="K26" t="n">
-        <v>102680.3</v>
+        <v>564392</v>
       </c>
       <c r="L26" t="n">
-        <v>431264</v>
+        <v>119554.7</v>
       </c>
       <c r="M26" t="n">
-        <v>512684.6</v>
+        <v>693673.7</v>
       </c>
       <c r="N26" t="n">
-        <v>90074</v>
+        <v>903424.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>453643.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>665340.5</v>
       </c>
     </row>
     <row r="27">
@@ -1978,28 +2142,34 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>119417.2</v>
+        <v>957213.1</v>
       </c>
       <c r="H27" t="n">
-        <v>172754.5</v>
+        <v>423137.9</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>833745</v>
       </c>
       <c r="J27" t="n">
-        <v>155851.5</v>
+        <v>402400.4</v>
       </c>
       <c r="K27" t="n">
-        <v>111942.5</v>
+        <v>27102</v>
       </c>
       <c r="L27" t="n">
-        <v>48609.1</v>
+        <v>535864</v>
       </c>
       <c r="M27" t="n">
-        <v>137088.4</v>
+        <v>288217.8</v>
       </c>
       <c r="N27" t="n">
-        <v>53842.3</v>
+        <v>45991</v>
+      </c>
+      <c r="O27" t="n">
+        <v>670486.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>750284.3</v>
       </c>
     </row>
     <row r="28">
@@ -2034,28 +2204,34 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>43823.1</v>
+        <v>336594.5</v>
       </c>
       <c r="H28" t="n">
-        <v>82824.8</v>
+        <v>211798.2</v>
       </c>
       <c r="I28" t="n">
-        <v>234810.9</v>
+        <v>703539.9</v>
       </c>
       <c r="J28" t="n">
-        <v>283269.5</v>
+        <v>295655.2</v>
       </c>
       <c r="K28" t="n">
-        <v>148765.9</v>
+        <v>642749.6</v>
       </c>
       <c r="L28" t="n">
-        <v>137385.6</v>
+        <v>762189.6</v>
       </c>
       <c r="M28" t="n">
-        <v>2079.9</v>
+        <v>945193.5</v>
       </c>
       <c r="N28" t="n">
-        <v>252491.9</v>
+        <v>796143.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>743140.1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>868092.1</v>
       </c>
     </row>
     <row r="29">
@@ -2090,28 +2266,34 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>431112.9</v>
+        <v>92745.8</v>
       </c>
       <c r="H29" t="n">
-        <v>215365</v>
+        <v>539296.1</v>
       </c>
       <c r="I29" t="n">
-        <v>325553.3</v>
+        <v>611677.8</v>
       </c>
       <c r="J29" t="n">
-        <v>150287.6</v>
+        <v>127287.8</v>
       </c>
       <c r="K29" t="n">
-        <v>347676.6</v>
+        <v>135699.5</v>
       </c>
       <c r="L29" t="n">
-        <v>88900.89999999999</v>
+        <v>185149.8</v>
       </c>
       <c r="M29" t="n">
-        <v>159636.9</v>
+        <v>813566</v>
       </c>
       <c r="N29" t="n">
-        <v>316487.9</v>
+        <v>293367.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>945974.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>721060.7</v>
       </c>
     </row>
     <row r="30">
@@ -2146,28 +2328,34 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>39100.9</v>
+        <v>96716.39999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>14022.2</v>
+        <v>729931.1</v>
       </c>
       <c r="I30" t="n">
-        <v>18257.1</v>
+        <v>987233.1</v>
       </c>
       <c r="J30" t="n">
-        <v>9998</v>
+        <v>420446.3</v>
       </c>
       <c r="K30" t="n">
-        <v>9004.6</v>
+        <v>461698.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1355.5</v>
+        <v>216384.6</v>
       </c>
       <c r="M30" t="n">
-        <v>47149.3</v>
+        <v>550096.6</v>
       </c>
       <c r="N30" t="n">
-        <v>39886.3</v>
+        <v>374841.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>419126.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>968398.6</v>
       </c>
     </row>
     <row r="31">
@@ -2202,28 +2390,34 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3467.2</v>
+        <v>847494.4</v>
       </c>
       <c r="H31" t="n">
-        <v>39754.3</v>
+        <v>201151.1</v>
       </c>
       <c r="I31" t="n">
-        <v>6967.6</v>
+        <v>653976.3</v>
       </c>
       <c r="J31" t="n">
-        <v>12641.6</v>
+        <v>940363.7</v>
       </c>
       <c r="K31" t="n">
-        <v>21162.2</v>
+        <v>50284.6</v>
       </c>
       <c r="L31" t="n">
-        <v>22458.8</v>
+        <v>484198.6</v>
       </c>
       <c r="M31" t="n">
-        <v>29116.4</v>
+        <v>454825.9</v>
       </c>
       <c r="N31" t="n">
-        <v>46175.6</v>
+        <v>145569.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>742269</v>
+      </c>
+      <c r="P31" t="n">
+        <v>600410.1</v>
       </c>
     </row>
     <row r="32">
@@ -2258,28 +2452,34 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>83706.7</v>
+        <v>603726</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>311716.3</v>
       </c>
       <c r="I32" t="n">
-        <v>140350.7</v>
+        <v>7823.1</v>
       </c>
       <c r="J32" t="n">
-        <v>118796.5</v>
+        <v>677317.9</v>
       </c>
       <c r="K32" t="n">
-        <v>21945.1</v>
+        <v>379103.9</v>
       </c>
       <c r="L32" t="n">
-        <v>132965.6</v>
+        <v>724585</v>
       </c>
       <c r="M32" t="n">
-        <v>122566.6</v>
+        <v>314517.2</v>
       </c>
       <c r="N32" t="n">
-        <v>129034.6</v>
+        <v>531166.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>154522.9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>351646.2</v>
       </c>
     </row>
     <row r="33">
@@ -2314,28 +2514,34 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>966827.7</v>
+        <v>807128.3</v>
       </c>
       <c r="H33" t="n">
-        <v>796332.9</v>
+        <v>995149.4</v>
       </c>
       <c r="I33" t="n">
-        <v>99057.3</v>
+        <v>817104.1</v>
       </c>
       <c r="J33" t="n">
-        <v>746979.6</v>
+        <v>902805.5</v>
       </c>
       <c r="K33" t="n">
-        <v>687820.6</v>
+        <v>211660.3</v>
       </c>
       <c r="L33" t="n">
-        <v>374432.5</v>
+        <v>976607</v>
       </c>
       <c r="M33" t="n">
-        <v>679715.7</v>
+        <v>323273.8</v>
       </c>
       <c r="N33" t="n">
-        <v>151169.6</v>
+        <v>565928.1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>414884.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>577918.5</v>
       </c>
     </row>
     <row r="34">
@@ -2370,28 +2576,34 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>144857.2</v>
+        <v>729731.8</v>
       </c>
       <c r="H34" t="n">
-        <v>276168.2</v>
+        <v>649878.1</v>
       </c>
       <c r="I34" t="n">
-        <v>249403.8</v>
+        <v>299378.8</v>
       </c>
       <c r="J34" t="n">
-        <v>104531.2</v>
+        <v>615514.9</v>
       </c>
       <c r="K34" t="n">
-        <v>235291.8</v>
+        <v>326845.8</v>
       </c>
       <c r="L34" t="n">
-        <v>104522.7</v>
+        <v>524636.9</v>
       </c>
       <c r="M34" t="n">
-        <v>216612.1</v>
+        <v>970184.7</v>
       </c>
       <c r="N34" t="n">
-        <v>20198.9</v>
+        <v>792519.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>99021.60000000001</v>
+      </c>
+      <c r="P34" t="n">
+        <v>212738.8</v>
       </c>
     </row>
     <row r="35">
@@ -2426,28 +2638,34 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>142178.9</v>
+        <v>536228.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>438100.1</v>
       </c>
       <c r="I35" t="n">
-        <v>21943.8</v>
+        <v>663388.7</v>
       </c>
       <c r="J35" t="n">
-        <v>185990.1</v>
+        <v>300949.9</v>
       </c>
       <c r="K35" t="n">
-        <v>103237.5</v>
+        <v>761229.7</v>
       </c>
       <c r="L35" t="n">
-        <v>66251.5</v>
+        <v>282998.7</v>
       </c>
       <c r="M35" t="n">
-        <v>92453.89999999999</v>
+        <v>404175.1</v>
       </c>
       <c r="N35" t="n">
-        <v>125981.7</v>
+        <v>169983.6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>489347</v>
+      </c>
+      <c r="P35" t="n">
+        <v>656736.3</v>
       </c>
     </row>
     <row r="36">
@@ -2482,28 +2700,34 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>131489</v>
+        <v>973115.8</v>
       </c>
       <c r="H36" t="n">
-        <v>147498.7</v>
+        <v>517575.8</v>
       </c>
       <c r="I36" t="n">
-        <v>89959</v>
+        <v>938930</v>
       </c>
       <c r="J36" t="n">
-        <v>969.7</v>
+        <v>547937.2</v>
       </c>
       <c r="K36" t="n">
-        <v>55726.7</v>
+        <v>379126.2</v>
       </c>
       <c r="L36" t="n">
-        <v>159217.9</v>
+        <v>100526.1</v>
       </c>
       <c r="M36" t="n">
-        <v>159916.5</v>
+        <v>514596.3</v>
       </c>
       <c r="N36" t="n">
-        <v>73209.3</v>
+        <v>78968.39999999999</v>
+      </c>
+      <c r="O36" t="n">
+        <v>408115.9</v>
+      </c>
+      <c r="P36" t="n">
+        <v>224244.9</v>
       </c>
     </row>
     <row r="37">
@@ -2538,28 +2762,34 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>34230.8</v>
+        <v>378534.4</v>
       </c>
       <c r="H37" t="n">
-        <v>146870.7</v>
+        <v>121004.2</v>
       </c>
       <c r="I37" t="n">
-        <v>94055.60000000001</v>
+        <v>134291.1</v>
       </c>
       <c r="J37" t="n">
-        <v>117793.6</v>
+        <v>405.9</v>
       </c>
       <c r="K37" t="n">
-        <v>105627.9</v>
+        <v>752009.8</v>
       </c>
       <c r="L37" t="n">
-        <v>51799.6</v>
+        <v>194117.6</v>
       </c>
       <c r="M37" t="n">
-        <v>240194</v>
+        <v>988119.2</v>
       </c>
       <c r="N37" t="n">
-        <v>177071</v>
+        <v>870839.6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>951521.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>108218.4</v>
       </c>
     </row>
     <row r="38">
@@ -2594,28 +2824,34 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>15666.2</v>
+        <v>552040.6</v>
       </c>
       <c r="H38" t="n">
-        <v>5856.3</v>
+        <v>224697.3</v>
       </c>
       <c r="I38" t="n">
-        <v>7076.5</v>
+        <v>115428.7</v>
       </c>
       <c r="J38" t="n">
-        <v>29825.3</v>
+        <v>286913.7</v>
       </c>
       <c r="K38" t="n">
-        <v>21157.7</v>
+        <v>831924.3</v>
       </c>
       <c r="L38" t="n">
-        <v>26873.6</v>
+        <v>227483.2</v>
       </c>
       <c r="M38" t="n">
-        <v>46535.4</v>
+        <v>657660.4</v>
       </c>
       <c r="N38" t="n">
-        <v>8351.6</v>
+        <v>619710.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>32716.3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>845373.4</v>
       </c>
     </row>
     <row r="39">
@@ -2650,28 +2886,34 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>187505</v>
+        <v>829404.7</v>
       </c>
       <c r="H39" t="n">
-        <v>619600.3</v>
+        <v>338085.6</v>
       </c>
       <c r="I39" t="n">
-        <v>951866</v>
+        <v>107036</v>
       </c>
       <c r="J39" t="n">
-        <v>195530.9</v>
+        <v>429888.1</v>
       </c>
       <c r="K39" t="n">
-        <v>561801.3</v>
+        <v>252271.5</v>
       </c>
       <c r="L39" t="n">
-        <v>409429.8</v>
+        <v>179441.5</v>
       </c>
       <c r="M39" t="n">
-        <v>710287.3</v>
+        <v>542593.6</v>
       </c>
       <c r="N39" t="n">
-        <v>167669.9</v>
+        <v>240829.8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>370530</v>
+      </c>
+      <c r="P39" t="n">
+        <v>367561.1</v>
       </c>
     </row>
     <row r="40">
@@ -2706,28 +2948,34 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>159192.5</v>
+        <v>618519.8</v>
       </c>
       <c r="H40" t="n">
-        <v>6616.4</v>
+        <v>588308.7</v>
       </c>
       <c r="I40" t="n">
-        <v>57791</v>
+        <v>553223.6</v>
       </c>
       <c r="J40" t="n">
-        <v>113164.8</v>
+        <v>579984.8</v>
       </c>
       <c r="K40" t="n">
-        <v>99103</v>
+        <v>81906.2</v>
       </c>
       <c r="L40" t="n">
-        <v>114577</v>
+        <v>14148.4</v>
       </c>
       <c r="M40" t="n">
-        <v>108657.8</v>
+        <v>413247.6</v>
       </c>
       <c r="N40" t="n">
-        <v>108445.3</v>
+        <v>912829</v>
+      </c>
+      <c r="O40" t="n">
+        <v>443383.1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>762605.6</v>
       </c>
     </row>
     <row r="41">
@@ -2762,28 +3010,34 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>380026.1</v>
+        <v>861706.9</v>
       </c>
       <c r="H41" t="n">
-        <v>109349.1</v>
+        <v>230114.7</v>
       </c>
       <c r="I41" t="n">
-        <v>368020.7</v>
+        <v>272348.2</v>
       </c>
       <c r="J41" t="n">
-        <v>123841.1</v>
+        <v>654705.6</v>
       </c>
       <c r="K41" t="n">
-        <v>16212</v>
+        <v>19383.3</v>
       </c>
       <c r="L41" t="n">
-        <v>431113.6</v>
+        <v>534135.1</v>
       </c>
       <c r="M41" t="n">
-        <v>432658.7</v>
+        <v>187582.5</v>
       </c>
       <c r="N41" t="n">
-        <v>405963.3</v>
+        <v>143117.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>950555.2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>574100</v>
       </c>
     </row>
     <row r="42">
@@ -2818,28 +3072,34 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>36883.3</v>
+        <v>577352.1</v>
       </c>
       <c r="H42" t="n">
-        <v>43053.8</v>
+        <v>220217.4</v>
       </c>
       <c r="I42" t="n">
-        <v>21414.1</v>
+        <v>604829.8</v>
       </c>
       <c r="J42" t="n">
-        <v>39244.6</v>
+        <v>464988.2</v>
       </c>
       <c r="K42" t="n">
-        <v>40274</v>
+        <v>539419</v>
       </c>
       <c r="L42" t="n">
-        <v>26618.7</v>
+        <v>274311.3</v>
       </c>
       <c r="M42" t="n">
-        <v>8427.200000000001</v>
+        <v>361779.4</v>
       </c>
       <c r="N42" t="n">
-        <v>14638.8</v>
+        <v>461149.9</v>
+      </c>
+      <c r="O42" t="n">
+        <v>855450.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>807221.4</v>
       </c>
     </row>
     <row r="43">
@@ -2874,28 +3134,34 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>190483.3</v>
+        <v>704571.8</v>
       </c>
       <c r="H43" t="n">
-        <v>180039</v>
+        <v>70993.10000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>27186.9</v>
+        <v>717612.2</v>
       </c>
       <c r="J43" t="n">
-        <v>82366.3</v>
+        <v>442159.8</v>
       </c>
       <c r="K43" t="n">
-        <v>55522.5</v>
+        <v>999907.8</v>
       </c>
       <c r="L43" t="n">
-        <v>140309.2</v>
+        <v>974294.9</v>
       </c>
       <c r="M43" t="n">
-        <v>29317</v>
+        <v>756443.2</v>
       </c>
       <c r="N43" t="n">
-        <v>49571.1</v>
+        <v>253977.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>99354.60000000001</v>
+      </c>
+      <c r="P43" t="n">
+        <v>845155.2</v>
       </c>
     </row>
     <row r="44">
@@ -2930,28 +3196,34 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>393004.4</v>
+        <v>45824.4</v>
       </c>
       <c r="H44" t="n">
-        <v>632585.8</v>
+        <v>631103</v>
       </c>
       <c r="I44" t="n">
-        <v>375484.7</v>
+        <v>203597.3</v>
       </c>
       <c r="J44" t="n">
-        <v>794701.3</v>
+        <v>213701.4</v>
       </c>
       <c r="K44" t="n">
-        <v>403149.3</v>
+        <v>349960.3</v>
       </c>
       <c r="L44" t="n">
-        <v>694856.3</v>
+        <v>553359</v>
       </c>
       <c r="M44" t="n">
-        <v>454968.3</v>
+        <v>625408.7</v>
       </c>
       <c r="N44" t="n">
-        <v>582164.6</v>
+        <v>255326.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>685680.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>974546.6</v>
       </c>
     </row>
     <row r="45">
@@ -2986,28 +3258,34 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>169445.7</v>
+        <v>227898.3</v>
       </c>
       <c r="H45" t="n">
-        <v>194432.3</v>
+        <v>228941.8</v>
       </c>
       <c r="I45" t="n">
-        <v>139482</v>
+        <v>634238</v>
       </c>
       <c r="J45" t="n">
-        <v>159151.9</v>
+        <v>473186.2</v>
       </c>
       <c r="K45" t="n">
-        <v>193628.3</v>
+        <v>650144.1</v>
       </c>
       <c r="L45" t="n">
-        <v>98983.39999999999</v>
+        <v>697417.4</v>
       </c>
       <c r="M45" t="n">
-        <v>56775.9</v>
+        <v>759990.5</v>
       </c>
       <c r="N45" t="n">
-        <v>26188.4</v>
+        <v>9397.4</v>
+      </c>
+      <c r="O45" t="n">
+        <v>544465.9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>818426.9</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3320,34 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>236501.7</v>
+        <v>289388</v>
       </c>
       <c r="H46" t="n">
-        <v>228688.1</v>
+        <v>905420</v>
       </c>
       <c r="I46" t="n">
-        <v>187872.5</v>
+        <v>263983.9</v>
       </c>
       <c r="J46" t="n">
-        <v>4933.6</v>
+        <v>901180.8</v>
       </c>
       <c r="K46" t="n">
-        <v>47437.2</v>
+        <v>781233</v>
       </c>
       <c r="L46" t="n">
-        <v>297551.9</v>
+        <v>126279.5</v>
       </c>
       <c r="M46" t="n">
-        <v>298708.4</v>
+        <v>203558.2</v>
       </c>
       <c r="N46" t="n">
-        <v>264650.2</v>
+        <v>804633.1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>977842.5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>613573.3</v>
       </c>
     </row>
     <row r="47">
@@ -3098,28 +3382,34 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>174894.7</v>
+        <v>79792</v>
       </c>
       <c r="H47" t="n">
-        <v>18740.5</v>
+        <v>859635.4</v>
       </c>
       <c r="I47" t="n">
-        <v>16557.5</v>
+        <v>488531.9</v>
       </c>
       <c r="J47" t="n">
-        <v>129810.3</v>
+        <v>796024.8</v>
       </c>
       <c r="K47" t="n">
-        <v>125150.8</v>
+        <v>651754.7</v>
       </c>
       <c r="L47" t="n">
-        <v>151066</v>
+        <v>868461.2</v>
       </c>
       <c r="M47" t="n">
-        <v>18312.5</v>
+        <v>549219.6</v>
       </c>
       <c r="N47" t="n">
-        <v>42747.2</v>
+        <v>901209.4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>358673.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>642699.2</v>
       </c>
     </row>
     <row r="48">
@@ -3154,28 +3444,34 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>296880.4</v>
+        <v>232790.9</v>
       </c>
       <c r="H48" t="n">
-        <v>222588.9</v>
+        <v>70857.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>905336.5</v>
       </c>
       <c r="J48" t="n">
-        <v>60384.8</v>
+        <v>169691.4</v>
       </c>
       <c r="K48" t="n">
-        <v>347046.1</v>
+        <v>754233.2</v>
       </c>
       <c r="L48" t="n">
-        <v>114550.5</v>
+        <v>490878.7</v>
       </c>
       <c r="M48" t="n">
-        <v>402997.8</v>
+        <v>927672.8</v>
       </c>
       <c r="N48" t="n">
-        <v>183844.1</v>
+        <v>677610.9</v>
+      </c>
+      <c r="O48" t="n">
+        <v>398139.6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>26253.8</v>
       </c>
     </row>
     <row r="49">
@@ -3210,28 +3506,34 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>191422.3</v>
+        <v>101001.4</v>
       </c>
       <c r="H49" t="n">
-        <v>437261.2</v>
+        <v>238004.6</v>
       </c>
       <c r="I49" t="n">
-        <v>338600.8</v>
+        <v>846103.7</v>
       </c>
       <c r="J49" t="n">
-        <v>281689.3</v>
+        <v>84795.5</v>
       </c>
       <c r="K49" t="n">
-        <v>82141.89999999999</v>
+        <v>949611.7</v>
       </c>
       <c r="L49" t="n">
-        <v>106606.4</v>
+        <v>872719.7</v>
       </c>
       <c r="M49" t="n">
-        <v>459955.1</v>
+        <v>438116.1</v>
       </c>
       <c r="N49" t="n">
-        <v>221247.7</v>
+        <v>157975.6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>189808.6</v>
+      </c>
+      <c r="P49" t="n">
+        <v>929084.3</v>
       </c>
     </row>
     <row r="50">
@@ -3266,28 +3568,34 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>179326.9</v>
+        <v>277973.6</v>
       </c>
       <c r="H50" t="n">
-        <v>24701.6</v>
+        <v>668977.8</v>
       </c>
       <c r="I50" t="n">
-        <v>70359</v>
+        <v>92298.5</v>
       </c>
       <c r="J50" t="n">
-        <v>158232</v>
+        <v>515452</v>
       </c>
       <c r="K50" t="n">
-        <v>128952.5</v>
+        <v>199360.7</v>
       </c>
       <c r="L50" t="n">
-        <v>120231.7</v>
+        <v>574064.2</v>
       </c>
       <c r="M50" t="n">
-        <v>57041.4</v>
+        <v>698250</v>
       </c>
       <c r="N50" t="n">
-        <v>5442.7</v>
+        <v>441729.8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>122159.7</v>
+      </c>
+      <c r="P50" t="n">
+        <v>829460.8</v>
       </c>
     </row>
     <row r="51">
@@ -3322,28 +3630,34 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>262754.4</v>
+        <v>635684.4</v>
       </c>
       <c r="H51" t="n">
-        <v>182097.7</v>
+        <v>214236.8</v>
       </c>
       <c r="I51" t="n">
-        <v>117555.7</v>
+        <v>423575.8</v>
       </c>
       <c r="J51" t="n">
-        <v>235151.3</v>
+        <v>632940.9</v>
       </c>
       <c r="K51" t="n">
-        <v>71840.39999999999</v>
+        <v>20380</v>
       </c>
       <c r="L51" t="n">
-        <v>72362.5</v>
+        <v>469396.9</v>
       </c>
       <c r="M51" t="n">
-        <v>21350</v>
+        <v>121426.1</v>
       </c>
       <c r="N51" t="n">
-        <v>3669.5</v>
+        <v>345565.6</v>
+      </c>
+      <c r="O51" t="n">
+        <v>848033.2</v>
+      </c>
+      <c r="P51" t="n">
+        <v>267447.7</v>
       </c>
     </row>
     <row r="52">
@@ -3378,28 +3692,34 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>94976</v>
+        <v>364832.2</v>
       </c>
       <c r="H52" t="n">
-        <v>251700</v>
+        <v>132311.8</v>
       </c>
       <c r="I52" t="n">
-        <v>163929.5</v>
+        <v>276680.2</v>
       </c>
       <c r="J52" t="n">
-        <v>141330.8</v>
+        <v>335188.3</v>
       </c>
       <c r="K52" t="n">
-        <v>21943.9</v>
+        <v>152382.3</v>
       </c>
       <c r="L52" t="n">
-        <v>4187.3</v>
+        <v>440468.8</v>
       </c>
       <c r="M52" t="n">
-        <v>276777.7</v>
+        <v>973146.8</v>
       </c>
       <c r="N52" t="n">
-        <v>119422.6</v>
+        <v>587571.7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>454717.4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>180416.1</v>
       </c>
     </row>
     <row r="53">
@@ -3434,28 +3754,34 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>356343.3</v>
+        <v>370181</v>
       </c>
       <c r="H53" t="n">
-        <v>211845.3</v>
+        <v>935514.2</v>
       </c>
       <c r="I53" t="n">
-        <v>320304.6</v>
+        <v>3545.7</v>
       </c>
       <c r="J53" t="n">
-        <v>76425</v>
+        <v>818423.5</v>
       </c>
       <c r="K53" t="n">
-        <v>39602.9</v>
+        <v>126221</v>
       </c>
       <c r="L53" t="n">
-        <v>487159.3</v>
+        <v>184363.7</v>
       </c>
       <c r="M53" t="n">
-        <v>163442.5</v>
+        <v>608871.7</v>
       </c>
       <c r="N53" t="n">
-        <v>381635.7</v>
+        <v>638938.7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>662768.7</v>
+      </c>
+      <c r="P53" t="n">
+        <v>702698.8</v>
       </c>
     </row>
     <row r="54">
@@ -3490,28 +3816,34 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>32161.3</v>
+        <v>209507</v>
       </c>
       <c r="H54" t="n">
-        <v>21879.9</v>
+        <v>571043.1</v>
       </c>
       <c r="I54" t="n">
-        <v>11939.5</v>
+        <v>771119.2</v>
       </c>
       <c r="J54" t="n">
-        <v>46232.1</v>
+        <v>751138.1</v>
       </c>
       <c r="K54" t="n">
-        <v>30618.7</v>
+        <v>669458.8</v>
       </c>
       <c r="L54" t="n">
-        <v>33307.3</v>
+        <v>51376.7</v>
       </c>
       <c r="M54" t="n">
-        <v>8790.5</v>
+        <v>239297.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>424308.9</v>
+      </c>
+      <c r="O54" t="n">
+        <v>641704.5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>308984.7</v>
       </c>
     </row>
     <row r="55">
@@ -3546,28 +3878,34 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5774.2</v>
+        <v>266977.8</v>
       </c>
       <c r="H55" t="n">
-        <v>173417.9</v>
+        <v>472671</v>
       </c>
       <c r="I55" t="n">
-        <v>411271.2</v>
+        <v>637113.4</v>
       </c>
       <c r="J55" t="n">
-        <v>185997.5</v>
+        <v>672795.7</v>
       </c>
       <c r="K55" t="n">
-        <v>436742.7</v>
+        <v>563969.6</v>
       </c>
       <c r="L55" t="n">
-        <v>59116.6</v>
+        <v>941063.6</v>
       </c>
       <c r="M55" t="n">
-        <v>167572</v>
+        <v>158378.2</v>
       </c>
       <c r="N55" t="n">
-        <v>261974.7</v>
+        <v>250098.2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>597146</v>
+      </c>
+      <c r="P55" t="n">
+        <v>339824.7</v>
       </c>
     </row>
     <row r="56">
@@ -3602,28 +3940,34 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>487527.8</v>
+        <v>936654.6</v>
       </c>
       <c r="H56" t="n">
-        <v>248124.2</v>
+        <v>784619.4</v>
       </c>
       <c r="I56" t="n">
-        <v>27814</v>
+        <v>261955.3</v>
       </c>
       <c r="J56" t="n">
-        <v>83524</v>
+        <v>224640.7</v>
       </c>
       <c r="K56" t="n">
-        <v>386687.1</v>
+        <v>217964.5</v>
       </c>
       <c r="L56" t="n">
-        <v>337092.8</v>
+        <v>477729.2</v>
       </c>
       <c r="M56" t="n">
-        <v>370415.9</v>
+        <v>550839</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>845303.9</v>
+      </c>
+      <c r="O56" t="n">
+        <v>21357.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>6105.8</v>
       </c>
     </row>
     <row r="57">
@@ -3658,28 +4002,34 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2536.6</v>
+        <v>648035.4</v>
       </c>
       <c r="H57" t="n">
-        <v>72846.2</v>
+        <v>807497</v>
       </c>
       <c r="I57" t="n">
-        <v>35857.9</v>
+        <v>741230.9</v>
       </c>
       <c r="J57" t="n">
-        <v>7149.9</v>
+        <v>199129.9</v>
       </c>
       <c r="K57" t="n">
-        <v>142827</v>
+        <v>699465</v>
       </c>
       <c r="L57" t="n">
-        <v>44965.1</v>
+        <v>822115.6</v>
       </c>
       <c r="M57" t="n">
-        <v>183177.7</v>
+        <v>552251.4</v>
       </c>
       <c r="N57" t="n">
-        <v>165213.3</v>
+        <v>199217</v>
+      </c>
+      <c r="O57" t="n">
+        <v>786794.6</v>
+      </c>
+      <c r="P57" t="n">
+        <v>869862.7</v>
       </c>
     </row>
     <row r="58">
@@ -3714,28 +4064,34 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>35864.3</v>
+        <v>609131</v>
       </c>
       <c r="H58" t="n">
-        <v>15849</v>
+        <v>190409.9</v>
       </c>
       <c r="I58" t="n">
-        <v>154756.5</v>
+        <v>551680.4</v>
       </c>
       <c r="J58" t="n">
-        <v>120307.4</v>
+        <v>24425.4</v>
       </c>
       <c r="K58" t="n">
-        <v>259816.4</v>
+        <v>766898.1</v>
       </c>
       <c r="L58" t="n">
-        <v>93243.8</v>
+        <v>400707.4</v>
       </c>
       <c r="M58" t="n">
-        <v>137051</v>
+        <v>93209.2</v>
       </c>
       <c r="N58" t="n">
-        <v>87513.89999999999</v>
+        <v>384693.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>243568.9</v>
+      </c>
+      <c r="P58" t="n">
+        <v>566321.1</v>
       </c>
     </row>
     <row r="59">
@@ -3770,28 +4126,34 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>369814</v>
+        <v>171138.6</v>
       </c>
       <c r="H59" t="n">
-        <v>184200</v>
+        <v>96930.8</v>
       </c>
       <c r="I59" t="n">
-        <v>498893.8</v>
+        <v>427686.9</v>
       </c>
       <c r="J59" t="n">
-        <v>366258.4</v>
+        <v>244842.5</v>
       </c>
       <c r="K59" t="n">
-        <v>398007.2</v>
+        <v>167789.1</v>
       </c>
       <c r="L59" t="n">
-        <v>466205.5</v>
+        <v>74082.2</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>992257.1</v>
       </c>
       <c r="N59" t="n">
-        <v>318007.3</v>
+        <v>483208.1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>125923.9</v>
+      </c>
+      <c r="P59" t="n">
+        <v>400784.3</v>
       </c>
     </row>
     <row r="60">
@@ -3826,28 +4188,34 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1998.2</v>
+        <v>729126.8</v>
       </c>
       <c r="H60" t="n">
-        <v>151805.1</v>
+        <v>431051.2</v>
       </c>
       <c r="I60" t="n">
-        <v>147637.5</v>
+        <v>9669.700000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>41102.5</v>
+        <v>475136.3</v>
       </c>
       <c r="K60" t="n">
-        <v>84009.60000000001</v>
+        <v>607247.5</v>
       </c>
       <c r="L60" t="n">
-        <v>194514</v>
+        <v>629445.7</v>
       </c>
       <c r="M60" t="n">
-        <v>56022.7</v>
+        <v>912929.9</v>
       </c>
       <c r="N60" t="n">
-        <v>46356</v>
+        <v>237205.7</v>
+      </c>
+      <c r="O60" t="n">
+        <v>564578</v>
+      </c>
+      <c r="P60" t="n">
+        <v>141874.7</v>
       </c>
     </row>
     <row r="61">
@@ -3882,28 +4250,34 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>123946.4</v>
+        <v>163402.5</v>
       </c>
       <c r="H61" t="n">
-        <v>137564.5</v>
+        <v>423578.6</v>
       </c>
       <c r="I61" t="n">
-        <v>174252.1</v>
+        <v>75243.89999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>191182.8</v>
+        <v>849737.7</v>
       </c>
       <c r="K61" t="n">
-        <v>177589.1</v>
+        <v>747925.7</v>
       </c>
       <c r="L61" t="n">
-        <v>198750.1</v>
+        <v>53609.1</v>
       </c>
       <c r="M61" t="n">
-        <v>87538.2</v>
+        <v>461447.9</v>
       </c>
       <c r="N61" t="n">
-        <v>277816.3</v>
+        <v>571922.7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>68610.2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>633172</v>
       </c>
     </row>
     <row r="62">
@@ -3938,28 +4312,34 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>249578.4</v>
+        <v>379455.4</v>
       </c>
       <c r="H62" t="n">
-        <v>135854.7</v>
+        <v>467024.7</v>
       </c>
       <c r="I62" t="n">
-        <v>283069.2</v>
+        <v>883106.4</v>
       </c>
       <c r="J62" t="n">
-        <v>231055.5</v>
+        <v>72828.2</v>
       </c>
       <c r="K62" t="n">
-        <v>31742</v>
+        <v>114532.9</v>
       </c>
       <c r="L62" t="n">
-        <v>94244.3</v>
+        <v>149197.6</v>
       </c>
       <c r="M62" t="n">
-        <v>107518.3</v>
+        <v>117466.1</v>
       </c>
       <c r="N62" t="n">
-        <v>135602.5</v>
+        <v>574811.9</v>
+      </c>
+      <c r="O62" t="n">
+        <v>765157.4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>30657.1</v>
       </c>
     </row>
     <row r="63">
@@ -3994,28 +4374,34 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>42625.6</v>
+        <v>989523.4</v>
       </c>
       <c r="H63" t="n">
-        <v>40381.8</v>
+        <v>729075.8</v>
       </c>
       <c r="I63" t="n">
-        <v>35238.2</v>
+        <v>903928.6</v>
       </c>
       <c r="J63" t="n">
-        <v>10758.9</v>
+        <v>414441</v>
       </c>
       <c r="K63" t="n">
-        <v>7424.7</v>
+        <v>819301.2</v>
       </c>
       <c r="L63" t="n">
-        <v>48420.3</v>
+        <v>562839.6</v>
       </c>
       <c r="M63" t="n">
-        <v>2457</v>
+        <v>832143.2</v>
       </c>
       <c r="N63" t="n">
-        <v>41006.3</v>
+        <v>992692</v>
+      </c>
+      <c r="O63" t="n">
+        <v>207157.4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>746111.8</v>
       </c>
     </row>
     <row r="64">
@@ -4050,28 +4436,34 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>47605.3</v>
+        <v>639999.8</v>
       </c>
       <c r="H64" t="n">
-        <v>27802.1</v>
+        <v>673364.5</v>
       </c>
       <c r="I64" t="n">
-        <v>4745.3</v>
+        <v>545590.3</v>
       </c>
       <c r="J64" t="n">
-        <v>39692.5</v>
+        <v>629765.4</v>
       </c>
       <c r="K64" t="n">
-        <v>3092.8</v>
+        <v>964720.8</v>
       </c>
       <c r="L64" t="n">
-        <v>11122.2</v>
+        <v>303835.5</v>
       </c>
       <c r="M64" t="n">
-        <v>20035.1</v>
+        <v>498375.5</v>
       </c>
       <c r="N64" t="n">
-        <v>46879.4</v>
+        <v>295230.8</v>
+      </c>
+      <c r="O64" t="n">
+        <v>215951.4</v>
+      </c>
+      <c r="P64" t="n">
+        <v>215132.9</v>
       </c>
     </row>
     <row r="65">
@@ -4106,28 +4498,34 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>175856.3</v>
+        <v>556949.7</v>
       </c>
       <c r="H65" t="n">
-        <v>22542.4</v>
+        <v>984165.2</v>
       </c>
       <c r="I65" t="n">
-        <v>59365.2</v>
+        <v>834595</v>
       </c>
       <c r="J65" t="n">
-        <v>242799.1</v>
+        <v>194435.2</v>
       </c>
       <c r="K65" t="n">
-        <v>254190.3</v>
+        <v>108098.7</v>
       </c>
       <c r="L65" t="n">
-        <v>36802.2</v>
+        <v>993918.1</v>
       </c>
       <c r="M65" t="n">
-        <v>15238.8</v>
+        <v>716603.3</v>
       </c>
       <c r="N65" t="n">
-        <v>129975.3</v>
+        <v>977944.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>869695.4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>419832.5</v>
       </c>
     </row>
     <row r="66">
@@ -4162,28 +4560,34 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>248113.6</v>
+        <v>684614.3</v>
       </c>
       <c r="H66" t="n">
-        <v>213389.3</v>
+        <v>98417.89999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>454161.3</v>
+        <v>582509.6</v>
       </c>
       <c r="J66" t="n">
-        <v>223061.1</v>
+        <v>696354.3</v>
       </c>
       <c r="K66" t="n">
-        <v>307091.9</v>
+        <v>25678.4</v>
       </c>
       <c r="L66" t="n">
-        <v>323674.5</v>
+        <v>118451.6</v>
       </c>
       <c r="M66" t="n">
-        <v>441401</v>
+        <v>508872</v>
       </c>
       <c r="N66" t="n">
-        <v>43952</v>
+        <v>658229.8</v>
+      </c>
+      <c r="O66" t="n">
+        <v>328559.6</v>
+      </c>
+      <c r="P66" t="n">
+        <v>340896</v>
       </c>
     </row>
     <row r="67">
@@ -4218,28 +4622,34 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>209675.5</v>
+        <v>842851.9</v>
       </c>
       <c r="H67" t="n">
-        <v>398619.3</v>
+        <v>402621.3</v>
       </c>
       <c r="I67" t="n">
-        <v>497044.2</v>
+        <v>148093.8</v>
       </c>
       <c r="J67" t="n">
-        <v>9863</v>
+        <v>494377.2</v>
       </c>
       <c r="K67" t="n">
-        <v>356714</v>
+        <v>311957.2</v>
       </c>
       <c r="L67" t="n">
-        <v>390739.4</v>
+        <v>764443.4</v>
       </c>
       <c r="M67" t="n">
-        <v>282869</v>
+        <v>273424.9</v>
       </c>
       <c r="N67" t="n">
-        <v>135290.8</v>
+        <v>274480.4</v>
+      </c>
+      <c r="O67" t="n">
+        <v>147554.2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>370053.1</v>
       </c>
     </row>
     <row r="68">
@@ -4274,28 +4684,34 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>775999.9</v>
       </c>
       <c r="H68" t="n">
-        <v>14748.8</v>
+        <v>339302.6</v>
       </c>
       <c r="I68" t="n">
-        <v>140538.2</v>
+        <v>127445.5</v>
       </c>
       <c r="J68" t="n">
-        <v>235895</v>
+        <v>243984.4</v>
       </c>
       <c r="K68" t="n">
-        <v>292036.1</v>
+        <v>677347.3</v>
       </c>
       <c r="L68" t="n">
-        <v>79896.39999999999</v>
+        <v>606317.7</v>
       </c>
       <c r="M68" t="n">
-        <v>120652.3</v>
+        <v>834723.9</v>
       </c>
       <c r="N68" t="n">
-        <v>395639.5</v>
+        <v>565929</v>
+      </c>
+      <c r="O68" t="n">
+        <v>900531</v>
+      </c>
+      <c r="P68" t="n">
+        <v>721596</v>
       </c>
     </row>
     <row r="69">
@@ -4330,28 +4746,34 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>382048.5</v>
+        <v>229048.1</v>
       </c>
       <c r="H69" t="n">
-        <v>287888.5</v>
+        <v>861672.5</v>
       </c>
       <c r="I69" t="n">
-        <v>194272.4</v>
+        <v>308258.3</v>
       </c>
       <c r="J69" t="n">
-        <v>495771.8</v>
+        <v>656058</v>
       </c>
       <c r="K69" t="n">
-        <v>118351.9</v>
+        <v>958172.8</v>
       </c>
       <c r="L69" t="n">
-        <v>369078.7</v>
+        <v>790740.8</v>
       </c>
       <c r="M69" t="n">
-        <v>295822.1</v>
+        <v>980244.6</v>
       </c>
       <c r="N69" t="n">
-        <v>175905.9</v>
+        <v>685799.5</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2835.6</v>
+      </c>
+      <c r="P69" t="n">
+        <v>776835.6</v>
       </c>
     </row>
     <row r="70">
@@ -4386,28 +4808,34 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>7113.7</v>
+        <v>32100.2</v>
       </c>
       <c r="H70" t="n">
-        <v>41836.5</v>
+        <v>248656.3</v>
       </c>
       <c r="I70" t="n">
-        <v>48519.7</v>
+        <v>898981.5</v>
       </c>
       <c r="J70" t="n">
-        <v>8786.1</v>
+        <v>5544.8</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>396654.4</v>
       </c>
       <c r="L70" t="n">
-        <v>30087.1</v>
+        <v>225687.1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>243730.9</v>
       </c>
       <c r="N70" t="n">
-        <v>16593.4</v>
+        <v>744668.8</v>
+      </c>
+      <c r="O70" t="n">
+        <v>858406.1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>567593.6</v>
       </c>
     </row>
     <row r="71">
@@ -4442,28 +4870,34 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>161304.6</v>
+        <v>315453</v>
       </c>
       <c r="H71" t="n">
-        <v>35557.8</v>
+        <v>190208.9</v>
       </c>
       <c r="I71" t="n">
-        <v>173654</v>
+        <v>796122.3</v>
       </c>
       <c r="J71" t="n">
-        <v>29610.6</v>
+        <v>750964.5</v>
       </c>
       <c r="K71" t="n">
-        <v>28399.2</v>
+        <v>715014.7</v>
       </c>
       <c r="L71" t="n">
-        <v>105296.9</v>
+        <v>522572.5</v>
       </c>
       <c r="M71" t="n">
-        <v>14580.5</v>
+        <v>551265.1</v>
       </c>
       <c r="N71" t="n">
-        <v>132454.9</v>
+        <v>49044.3</v>
+      </c>
+      <c r="O71" t="n">
+        <v>144688</v>
+      </c>
+      <c r="P71" t="n">
+        <v>84957</v>
       </c>
     </row>
     <row r="72">
@@ -4498,28 +4932,34 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>336892.8</v>
+        <v>267740.9</v>
       </c>
       <c r="H72" t="n">
-        <v>975872.7</v>
+        <v>448613.5</v>
       </c>
       <c r="I72" t="n">
-        <v>437149.9</v>
+        <v>860702.6</v>
       </c>
       <c r="J72" t="n">
-        <v>487456.4</v>
+        <v>770046.2</v>
       </c>
       <c r="K72" t="n">
-        <v>707329.3</v>
+        <v>75996.5</v>
       </c>
       <c r="L72" t="n">
-        <v>889655.4</v>
+        <v>450514.5</v>
       </c>
       <c r="M72" t="n">
-        <v>357147.1</v>
+        <v>383586</v>
       </c>
       <c r="N72" t="n">
-        <v>814547</v>
+        <v>606406.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>129992.1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>52608.8</v>
       </c>
     </row>
     <row r="73">
@@ -4554,28 +4994,34 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>734128</v>
+        <v>210982.8</v>
       </c>
       <c r="H73" t="n">
-        <v>178119.4</v>
+        <v>421881.6</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>898924.6</v>
       </c>
       <c r="J73" t="n">
-        <v>573048.4</v>
+        <v>106587.3</v>
       </c>
       <c r="K73" t="n">
-        <v>770945</v>
+        <v>690614.4</v>
       </c>
       <c r="L73" t="n">
-        <v>182490.7</v>
+        <v>442721</v>
       </c>
       <c r="M73" t="n">
-        <v>808902.5</v>
+        <v>921868.1</v>
       </c>
       <c r="N73" t="n">
-        <v>639826.9</v>
+        <v>496727.3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>250654.2</v>
+      </c>
+      <c r="P73" t="n">
+        <v>157409.9</v>
       </c>
     </row>
     <row r="74">
@@ -4610,28 +5056,34 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>24814.3</v>
+        <v>942909.7</v>
       </c>
       <c r="H74" t="n">
-        <v>3899.6</v>
+        <v>278545.1</v>
       </c>
       <c r="I74" t="n">
-        <v>15982.7</v>
+        <v>210076.5</v>
       </c>
       <c r="J74" t="n">
-        <v>48154.4</v>
+        <v>425146.2</v>
       </c>
       <c r="K74" t="n">
-        <v>33504.5</v>
+        <v>627242.4</v>
       </c>
       <c r="L74" t="n">
-        <v>16794.1</v>
+        <v>860166.7</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>508240.9</v>
       </c>
       <c r="N74" t="n">
-        <v>34661.9</v>
+        <v>904155.3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>174497.1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>617838.2</v>
       </c>
     </row>
     <row r="75">
@@ -4666,28 +5118,34 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>39353.1</v>
+        <v>876367.6</v>
       </c>
       <c r="H75" t="n">
-        <v>2416.9</v>
+        <v>249806.4</v>
       </c>
       <c r="I75" t="n">
-        <v>20988.5</v>
+        <v>249529.7</v>
       </c>
       <c r="J75" t="n">
-        <v>20706.8</v>
+        <v>175886.7</v>
       </c>
       <c r="K75" t="n">
-        <v>17568</v>
+        <v>101901.3</v>
       </c>
       <c r="L75" t="n">
-        <v>41442.1</v>
+        <v>990031.3</v>
       </c>
       <c r="M75" t="n">
-        <v>28907</v>
+        <v>879326.3</v>
       </c>
       <c r="N75" t="n">
-        <v>11286.9</v>
+        <v>286194.2</v>
+      </c>
+      <c r="O75" t="n">
+        <v>661057.6</v>
+      </c>
+      <c r="P75" t="n">
+        <v>673968.7</v>
       </c>
     </row>
     <row r="76">
@@ -4722,28 +5180,34 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>159855</v>
+        <v>314677.9</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>923265.6</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>102793.6</v>
       </c>
       <c r="J76" t="n">
-        <v>21016.6</v>
+        <v>957966</v>
       </c>
       <c r="K76" t="n">
-        <v>177595.2</v>
+        <v>772480.9</v>
       </c>
       <c r="L76" t="n">
-        <v>15074.5</v>
+        <v>305380.2</v>
       </c>
       <c r="M76" t="n">
-        <v>195610.1</v>
+        <v>864026.9</v>
       </c>
       <c r="N76" t="n">
-        <v>197056.4</v>
+        <v>798860.1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>25780.1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>272102.8</v>
       </c>
     </row>
     <row r="77">
@@ -4778,28 +5242,34 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>704652.4</v>
+        <v>655438.7</v>
       </c>
       <c r="H77" t="n">
-        <v>653808.4</v>
+        <v>443130.7</v>
       </c>
       <c r="I77" t="n">
-        <v>434483.3</v>
+        <v>780116.2</v>
       </c>
       <c r="J77" t="n">
-        <v>331429</v>
+        <v>517957.8</v>
       </c>
       <c r="K77" t="n">
-        <v>409575.2</v>
+        <v>850293.2</v>
       </c>
       <c r="L77" t="n">
-        <v>925610.8</v>
+        <v>621027.3</v>
       </c>
       <c r="M77" t="n">
-        <v>660767.6</v>
+        <v>276247.4</v>
       </c>
       <c r="N77" t="n">
-        <v>96368</v>
+        <v>607065</v>
+      </c>
+      <c r="O77" t="n">
+        <v>14860.3</v>
+      </c>
+      <c r="P77" t="n">
+        <v>661938.7</v>
       </c>
     </row>
     <row r="78">
@@ -4834,28 +5304,34 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>549887.8</v>
+        <v>395631.9</v>
       </c>
       <c r="H78" t="n">
-        <v>54977.6</v>
+        <v>861349.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>884134.7</v>
       </c>
       <c r="J78" t="n">
-        <v>823985.4</v>
+        <v>50218.4</v>
       </c>
       <c r="K78" t="n">
-        <v>480588.2</v>
+        <v>600411.6</v>
       </c>
       <c r="L78" t="n">
-        <v>207349.5</v>
+        <v>609630.9</v>
       </c>
       <c r="M78" t="n">
-        <v>977069.2</v>
+        <v>790006.2</v>
       </c>
       <c r="N78" t="n">
-        <v>115951.2</v>
+        <v>352321</v>
+      </c>
+      <c r="O78" t="n">
+        <v>789984.7</v>
+      </c>
+      <c r="P78" t="n">
+        <v>485661.7</v>
       </c>
     </row>
     <row r="79">
@@ -4890,28 +5366,34 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>94231.2</v>
+        <v>914547.6</v>
       </c>
       <c r="H79" t="n">
-        <v>53059.7</v>
+        <v>550325.3</v>
       </c>
       <c r="I79" t="n">
-        <v>77554.39999999999</v>
+        <v>406377.4</v>
       </c>
       <c r="J79" t="n">
-        <v>76338.5</v>
+        <v>249198.3</v>
       </c>
       <c r="K79" t="n">
-        <v>8999.799999999999</v>
+        <v>121055.1</v>
       </c>
       <c r="L79" t="n">
-        <v>52739.1</v>
+        <v>740089.3</v>
       </c>
       <c r="M79" t="n">
-        <v>112884.2</v>
+        <v>414942.4</v>
       </c>
       <c r="N79" t="n">
-        <v>139318.5</v>
+        <v>636617.9</v>
+      </c>
+      <c r="O79" t="n">
+        <v>237931.6</v>
+      </c>
+      <c r="P79" t="n">
+        <v>442044.2</v>
       </c>
     </row>
     <row r="80">
@@ -4946,28 +5428,34 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>200458.9</v>
+        <v>458851.9</v>
       </c>
       <c r="H80" t="n">
-        <v>124225.3</v>
+        <v>50588.3</v>
       </c>
       <c r="I80" t="n">
-        <v>68292.5</v>
+        <v>620661.5</v>
       </c>
       <c r="J80" t="n">
-        <v>116162.5</v>
+        <v>848336.3</v>
       </c>
       <c r="K80" t="n">
-        <v>289690</v>
+        <v>983844.4</v>
       </c>
       <c r="L80" t="n">
-        <v>280911.6</v>
+        <v>947590.2</v>
       </c>
       <c r="M80" t="n">
-        <v>70730.8</v>
+        <v>934248.4</v>
       </c>
       <c r="N80" t="n">
-        <v>118471.6</v>
+        <v>620891.2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>323771.5</v>
+      </c>
+      <c r="P80" t="n">
+        <v>273166.8</v>
       </c>
     </row>
     <row r="81">
@@ -5002,28 +5490,34 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>7022.9</v>
+        <v>264880.2</v>
       </c>
       <c r="H81" t="n">
-        <v>103402.1</v>
+        <v>999282.5</v>
       </c>
       <c r="I81" t="n">
-        <v>196552.3</v>
+        <v>154553.3</v>
       </c>
       <c r="J81" t="n">
-        <v>189855</v>
+        <v>456461.8</v>
       </c>
       <c r="K81" t="n">
-        <v>189816.4</v>
+        <v>782635.3</v>
       </c>
       <c r="L81" t="n">
-        <v>42441.1</v>
+        <v>207787.9</v>
       </c>
       <c r="M81" t="n">
-        <v>8611.799999999999</v>
+        <v>507737.7</v>
       </c>
       <c r="N81" t="n">
-        <v>136650.4</v>
+        <v>677764.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>174246.2</v>
+      </c>
+      <c r="P81" t="n">
+        <v>754943.1</v>
       </c>
     </row>
     <row r="82">
@@ -5058,28 +5552,34 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>164527</v>
+        <v>246627.5</v>
       </c>
       <c r="H82" t="n">
-        <v>119041.9</v>
+        <v>836027.6</v>
       </c>
       <c r="I82" t="n">
-        <v>145442.4</v>
+        <v>929881</v>
       </c>
       <c r="J82" t="n">
-        <v>17478.5</v>
+        <v>801416.6</v>
       </c>
       <c r="K82" t="n">
-        <v>110446.7</v>
+        <v>347203.8</v>
       </c>
       <c r="L82" t="n">
-        <v>103976.1</v>
+        <v>211025.2</v>
       </c>
       <c r="M82" t="n">
-        <v>2551.8</v>
+        <v>820549.5</v>
       </c>
       <c r="N82" t="n">
-        <v>117548.2</v>
+        <v>720928.4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>52399</v>
+      </c>
+      <c r="P82" t="n">
+        <v>113817.5</v>
       </c>
     </row>
     <row r="83">
@@ -5114,28 +5614,34 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>112962.6</v>
+        <v>561368.1</v>
       </c>
       <c r="H83" t="n">
-        <v>566810.6</v>
+        <v>968996.3</v>
       </c>
       <c r="I83" t="n">
-        <v>964849.2</v>
+        <v>864605.7</v>
       </c>
       <c r="J83" t="n">
-        <v>106082</v>
+        <v>667577.7</v>
       </c>
       <c r="K83" t="n">
-        <v>785852.8</v>
+        <v>428378</v>
       </c>
       <c r="L83" t="n">
-        <v>880195.7</v>
+        <v>660428.1</v>
       </c>
       <c r="M83" t="n">
-        <v>264504.6</v>
+        <v>282839</v>
       </c>
       <c r="N83" t="n">
-        <v>572237.2</v>
+        <v>659181.5</v>
+      </c>
+      <c r="O83" t="n">
+        <v>741718.1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>429913.6</v>
       </c>
     </row>
     <row r="84">
@@ -5170,28 +5676,34 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>86182.60000000001</v>
+        <v>262741.6</v>
       </c>
       <c r="H84" t="n">
-        <v>309160.4</v>
+        <v>926367</v>
       </c>
       <c r="I84" t="n">
-        <v>200919.8</v>
+        <v>976206</v>
       </c>
       <c r="J84" t="n">
-        <v>439490.9</v>
+        <v>987892.5</v>
       </c>
       <c r="K84" t="n">
-        <v>24740.6</v>
+        <v>370570.9</v>
       </c>
       <c r="L84" t="n">
-        <v>134365.3</v>
+        <v>157057.1</v>
       </c>
       <c r="M84" t="n">
-        <v>168999.3</v>
+        <v>298555.8</v>
       </c>
       <c r="N84" t="n">
-        <v>155543.6</v>
+        <v>838337.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>526085.5</v>
+      </c>
+      <c r="P84" t="n">
+        <v>283246.5</v>
       </c>
     </row>
     <row r="85">
@@ -5226,28 +5738,34 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>429131.6</v>
+        <v>584586</v>
       </c>
       <c r="H85" t="n">
-        <v>486251.1</v>
+        <v>848695.7</v>
       </c>
       <c r="I85" t="n">
-        <v>150310.2</v>
+        <v>810771.7</v>
       </c>
       <c r="J85" t="n">
-        <v>387038</v>
+        <v>595452.3</v>
       </c>
       <c r="K85" t="n">
-        <v>364426.8</v>
+        <v>505960.8</v>
       </c>
       <c r="L85" t="n">
-        <v>44734.5</v>
+        <v>173813.5</v>
       </c>
       <c r="M85" t="n">
-        <v>456725.1</v>
+        <v>586937.7</v>
       </c>
       <c r="N85" t="n">
-        <v>242281.7</v>
+        <v>628248.1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>745665.3</v>
+      </c>
+      <c r="P85" t="n">
+        <v>678486.3</v>
       </c>
     </row>
     <row r="86">
@@ -5282,28 +5800,34 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>374223.3</v>
+        <v>897822.9</v>
       </c>
       <c r="H86" t="n">
-        <v>791594.6</v>
+        <v>166311.1</v>
       </c>
       <c r="I86" t="n">
-        <v>709714.6</v>
+        <v>881416.2</v>
       </c>
       <c r="J86" t="n">
-        <v>780626.2</v>
+        <v>950039.6</v>
       </c>
       <c r="K86" t="n">
-        <v>568888</v>
+        <v>341231.2</v>
       </c>
       <c r="L86" t="n">
-        <v>875243</v>
+        <v>75064.89999999999</v>
       </c>
       <c r="M86" t="n">
-        <v>58098.7</v>
+        <v>998902.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>903403.7</v>
+      </c>
+      <c r="O86" t="n">
+        <v>476246</v>
+      </c>
+      <c r="P86" t="n">
+        <v>486632.8</v>
       </c>
     </row>
     <row r="87">
@@ -5338,28 +5862,34 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>72126.2</v>
+        <v>399400.5</v>
       </c>
       <c r="H87" t="n">
-        <v>73720.89999999999</v>
+        <v>485641.1</v>
       </c>
       <c r="I87" t="n">
-        <v>79436.7</v>
+        <v>24786.4</v>
       </c>
       <c r="J87" t="n">
-        <v>136260.4</v>
+        <v>891425.9</v>
       </c>
       <c r="K87" t="n">
-        <v>97798.2</v>
+        <v>849575.6</v>
       </c>
       <c r="L87" t="n">
-        <v>192107.2</v>
+        <v>2675.7</v>
       </c>
       <c r="M87" t="n">
-        <v>110302.6</v>
+        <v>489640.3</v>
       </c>
       <c r="N87" t="n">
-        <v>167543.7</v>
+        <v>646340.6</v>
+      </c>
+      <c r="O87" t="n">
+        <v>778017</v>
+      </c>
+      <c r="P87" t="n">
+        <v>667132.6</v>
       </c>
     </row>
     <row r="88">
@@ -5394,28 +5924,34 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>249269.5</v>
+        <v>219320.8</v>
       </c>
       <c r="H88" t="n">
-        <v>8283.799999999999</v>
+        <v>213747.3</v>
       </c>
       <c r="I88" t="n">
-        <v>256153.7</v>
+        <v>736564.5</v>
       </c>
       <c r="J88" t="n">
-        <v>64334.9</v>
+        <v>612652.3</v>
       </c>
       <c r="K88" t="n">
-        <v>67572.39999999999</v>
+        <v>822330.9</v>
       </c>
       <c r="L88" t="n">
-        <v>195493.6</v>
+        <v>450503.7</v>
       </c>
       <c r="M88" t="n">
-        <v>259395.7</v>
+        <v>148595.4</v>
       </c>
       <c r="N88" t="n">
-        <v>204675.8</v>
+        <v>308932.9</v>
+      </c>
+      <c r="O88" t="n">
+        <v>513238</v>
+      </c>
+      <c r="P88" t="n">
+        <v>45417.4</v>
       </c>
     </row>
     <row r="89">
@@ -5450,28 +5986,34 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>26532.2</v>
+        <v>997537.6</v>
       </c>
       <c r="H89" t="n">
-        <v>160188.9</v>
+        <v>401040.3</v>
       </c>
       <c r="I89" t="n">
-        <v>121700.1</v>
+        <v>332185.5</v>
       </c>
       <c r="J89" t="n">
-        <v>142571.1</v>
+        <v>719274</v>
       </c>
       <c r="K89" t="n">
-        <v>55133.7</v>
+        <v>105538.9</v>
       </c>
       <c r="L89" t="n">
-        <v>170329.1</v>
+        <v>593811.2</v>
       </c>
       <c r="M89" t="n">
-        <v>43704.4</v>
+        <v>538580.6</v>
       </c>
       <c r="N89" t="n">
-        <v>104165.9</v>
+        <v>440823.2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>109054</v>
+      </c>
+      <c r="P89" t="n">
+        <v>395263.4</v>
       </c>
     </row>
     <row r="90">
@@ -5506,28 +6048,34 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>292285.1</v>
+        <v>509526.3</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>58635.4</v>
       </c>
       <c r="I90" t="n">
-        <v>483246.1</v>
+        <v>930815.9</v>
       </c>
       <c r="J90" t="n">
-        <v>280772.4</v>
+        <v>504778.2</v>
       </c>
       <c r="K90" t="n">
-        <v>141410.2</v>
+        <v>960787.6</v>
       </c>
       <c r="L90" t="n">
-        <v>240921</v>
+        <v>291259.3</v>
       </c>
       <c r="M90" t="n">
-        <v>138314</v>
+        <v>345123.9</v>
       </c>
       <c r="N90" t="n">
-        <v>138514.8</v>
+        <v>579573.8</v>
+      </c>
+      <c r="O90" t="n">
+        <v>503838.7</v>
+      </c>
+      <c r="P90" t="n">
+        <v>599325</v>
       </c>
     </row>
     <row r="91">
@@ -5562,28 +6110,34 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>952211.7</v>
+        <v>90909.39999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>188765.9</v>
+        <v>378973.1</v>
       </c>
       <c r="I91" t="n">
-        <v>240681.9</v>
+        <v>802235.1</v>
       </c>
       <c r="J91" t="n">
-        <v>857386.7</v>
+        <v>830569.2</v>
       </c>
       <c r="K91" t="n">
-        <v>404396.4</v>
+        <v>635585.1</v>
       </c>
       <c r="L91" t="n">
-        <v>140359.5</v>
+        <v>231476.2</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>551917.4</v>
       </c>
       <c r="N91" t="n">
-        <v>295956.8</v>
+        <v>732359.8</v>
+      </c>
+      <c r="O91" t="n">
+        <v>945415.6</v>
+      </c>
+      <c r="P91" t="n">
+        <v>7687.1</v>
       </c>
     </row>
     <row r="92">
@@ -5618,28 +6172,34 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>404896.6</v>
+        <v>47116.4</v>
       </c>
       <c r="H92" t="n">
-        <v>583232.2</v>
+        <v>985308.8</v>
       </c>
       <c r="I92" t="n">
-        <v>816106.7</v>
+        <v>864064</v>
       </c>
       <c r="J92" t="n">
-        <v>713512.6</v>
+        <v>547872</v>
       </c>
       <c r="K92" t="n">
-        <v>638494.4</v>
+        <v>828707.3</v>
       </c>
       <c r="L92" t="n">
-        <v>940697.6</v>
+        <v>706955.8</v>
       </c>
       <c r="M92" t="n">
-        <v>300544.7</v>
+        <v>543430.1</v>
       </c>
       <c r="N92" t="n">
-        <v>657785.9</v>
+        <v>90133.39999999999</v>
+      </c>
+      <c r="O92" t="n">
+        <v>43365</v>
+      </c>
+      <c r="P92" t="n">
+        <v>301419.4</v>
       </c>
     </row>
     <row r="93">
@@ -5674,28 +6234,34 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>88170.5</v>
+        <v>109649.1</v>
       </c>
       <c r="H93" t="n">
-        <v>222288.6</v>
+        <v>265203.1</v>
       </c>
       <c r="I93" t="n">
-        <v>167731.5</v>
+        <v>810749.3</v>
       </c>
       <c r="J93" t="n">
-        <v>284079.7</v>
+        <v>897208.1</v>
       </c>
       <c r="K93" t="n">
-        <v>196347.7</v>
+        <v>707308.6</v>
       </c>
       <c r="L93" t="n">
-        <v>67037.2</v>
+        <v>702987.6</v>
       </c>
       <c r="M93" t="n">
-        <v>126170.7</v>
+        <v>455344.6</v>
       </c>
       <c r="N93" t="n">
-        <v>111536.1</v>
+        <v>295110.5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>783227</v>
+      </c>
+      <c r="P93" t="n">
+        <v>211234</v>
       </c>
     </row>
     <row r="94">
@@ -5730,28 +6296,34 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>139155</v>
+        <v>627446</v>
       </c>
       <c r="H94" t="n">
-        <v>16150.4</v>
+        <v>784070.6</v>
       </c>
       <c r="I94" t="n">
-        <v>174114.9</v>
+        <v>266805.7</v>
       </c>
       <c r="J94" t="n">
-        <v>141692.3</v>
+        <v>743655.4</v>
       </c>
       <c r="K94" t="n">
-        <v>35988.8</v>
+        <v>435487.1</v>
       </c>
       <c r="L94" t="n">
-        <v>158975.1</v>
+        <v>454031.3</v>
       </c>
       <c r="M94" t="n">
-        <v>261261.2</v>
+        <v>321777.4</v>
       </c>
       <c r="N94" t="n">
-        <v>297704.7</v>
+        <v>747480.9</v>
+      </c>
+      <c r="O94" t="n">
+        <v>866980.9</v>
+      </c>
+      <c r="P94" t="n">
+        <v>137234.8</v>
       </c>
     </row>
     <row r="95">
@@ -5786,28 +6358,34 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>296158.1</v>
+        <v>792079.4</v>
       </c>
       <c r="H95" t="n">
-        <v>295995.4</v>
+        <v>455008.4</v>
       </c>
       <c r="I95" t="n">
-        <v>258725.1</v>
+        <v>787374.5</v>
       </c>
       <c r="J95" t="n">
-        <v>24289.4</v>
+        <v>474674.4</v>
       </c>
       <c r="K95" t="n">
-        <v>295992.8</v>
+        <v>733795.3</v>
       </c>
       <c r="L95" t="n">
-        <v>17451.2</v>
+        <v>687384.9</v>
       </c>
       <c r="M95" t="n">
-        <v>62854.2</v>
+        <v>188652.4</v>
       </c>
       <c r="N95" t="n">
-        <v>172904.9</v>
+        <v>175640.1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>521451.2</v>
+      </c>
+      <c r="P95" t="n">
+        <v>255519.5</v>
       </c>
     </row>
     <row r="96">
@@ -5842,28 +6420,34 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>39262.7</v>
+        <v>422160</v>
       </c>
       <c r="H96" t="n">
-        <v>6479</v>
+        <v>423007.5</v>
       </c>
       <c r="I96" t="n">
-        <v>21476.2</v>
+        <v>108095.6</v>
       </c>
       <c r="J96" t="n">
-        <v>23875.2</v>
+        <v>259191.5</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>965473.7</v>
       </c>
       <c r="L96" t="n">
-        <v>36535.6</v>
+        <v>923911</v>
       </c>
       <c r="M96" t="n">
-        <v>44601.4</v>
+        <v>697498.4</v>
       </c>
       <c r="N96" t="n">
-        <v>26556.4</v>
+        <v>132159.8</v>
+      </c>
+      <c r="O96" t="n">
+        <v>458042.5</v>
+      </c>
+      <c r="P96" t="n">
+        <v>328122.4</v>
       </c>
     </row>
     <row r="97">
@@ -5898,28 +6482,34 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>63527.7</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>957317.6</v>
       </c>
       <c r="I97" t="n">
-        <v>67918.39999999999</v>
+        <v>872166.8</v>
       </c>
       <c r="J97" t="n">
-        <v>93662.10000000001</v>
+        <v>247239.7</v>
       </c>
       <c r="K97" t="n">
-        <v>151025.8</v>
+        <v>270082.4</v>
       </c>
       <c r="L97" t="n">
-        <v>19632.8</v>
+        <v>787828</v>
       </c>
       <c r="M97" t="n">
-        <v>284541.6</v>
+        <v>571797.6</v>
       </c>
       <c r="N97" t="n">
-        <v>156110.5</v>
+        <v>539407.8</v>
+      </c>
+      <c r="O97" t="n">
+        <v>964026.2</v>
+      </c>
+      <c r="P97" t="n">
+        <v>7729.9</v>
       </c>
     </row>
     <row r="98">
@@ -5954,28 +6544,34 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>130127.9</v>
+        <v>381619.3</v>
       </c>
       <c r="H98" t="n">
-        <v>40180.1</v>
+        <v>995422.7</v>
       </c>
       <c r="I98" t="n">
-        <v>147079.1</v>
+        <v>858593.3</v>
       </c>
       <c r="J98" t="n">
-        <v>49506.8</v>
+        <v>637661.4</v>
       </c>
       <c r="K98" t="n">
-        <v>243611.9</v>
+        <v>808199.2</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>625058</v>
       </c>
       <c r="M98" t="n">
-        <v>295464.6</v>
+        <v>233562.4</v>
       </c>
       <c r="N98" t="n">
-        <v>6622.9</v>
+        <v>971489.6</v>
+      </c>
+      <c r="O98" t="n">
+        <v>60825.4</v>
+      </c>
+      <c r="P98" t="n">
+        <v>747014.1</v>
       </c>
     </row>
     <row r="99">
@@ -6010,28 +6606,34 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>6166.9</v>
+        <v>996121.4</v>
       </c>
       <c r="H99" t="n">
-        <v>39608.4</v>
+        <v>555768.3</v>
       </c>
       <c r="I99" t="n">
-        <v>32019.7</v>
+        <v>222433.7</v>
       </c>
       <c r="J99" t="n">
-        <v>31160.5</v>
+        <v>765813.7</v>
       </c>
       <c r="K99" t="n">
-        <v>2407.5</v>
+        <v>538172.9</v>
       </c>
       <c r="L99" t="n">
-        <v>41807.6</v>
+        <v>661183</v>
       </c>
       <c r="M99" t="n">
-        <v>5798.3</v>
+        <v>775544.5</v>
       </c>
       <c r="N99" t="n">
-        <v>6188.5</v>
+        <v>530852.4</v>
+      </c>
+      <c r="O99" t="n">
+        <v>478981.9</v>
+      </c>
+      <c r="P99" t="n">
+        <v>175694.8</v>
       </c>
     </row>
     <row r="100">
@@ -6066,28 +6668,34 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>702017.3</v>
+        <v>529114.3</v>
       </c>
       <c r="H100" t="n">
-        <v>685897.2</v>
+        <v>718408.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>816586.6</v>
       </c>
       <c r="J100" t="n">
-        <v>101429.4</v>
+        <v>521299.8</v>
       </c>
       <c r="K100" t="n">
-        <v>622986.4</v>
+        <v>483497.5</v>
       </c>
       <c r="L100" t="n">
-        <v>419116.3</v>
+        <v>933668.5</v>
       </c>
       <c r="M100" t="n">
-        <v>511829</v>
+        <v>43647.3</v>
       </c>
       <c r="N100" t="n">
-        <v>283065.4</v>
+        <v>913487</v>
+      </c>
+      <c r="O100" t="n">
+        <v>401617.3</v>
+      </c>
+      <c r="P100" t="n">
+        <v>380207.4</v>
       </c>
     </row>
     <row r="101">
@@ -6122,28 +6730,34 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>248919.8</v>
+        <v>971078.4</v>
       </c>
       <c r="H101" t="n">
-        <v>389001.7</v>
+        <v>154796.8</v>
       </c>
       <c r="I101" t="n">
-        <v>486562.5</v>
+        <v>460303.2</v>
       </c>
       <c r="J101" t="n">
-        <v>204937.1</v>
+        <v>626748.4</v>
       </c>
       <c r="K101" t="n">
-        <v>274114.6</v>
+        <v>435574.5</v>
       </c>
       <c r="L101" t="n">
-        <v>344133.1</v>
+        <v>425139</v>
       </c>
       <c r="M101" t="n">
-        <v>117329.2</v>
+        <v>744705.2</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>830472.6</v>
+      </c>
+      <c r="O101" t="n">
+        <v>686097.5</v>
+      </c>
+      <c r="P101" t="n">
+        <v>703671.3</v>
       </c>
     </row>
     <row r="102">
@@ -6178,28 +6792,34 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>22157.3</v>
+        <v>860779.7</v>
       </c>
       <c r="H102" t="n">
-        <v>98861.3</v>
+        <v>296707.8</v>
       </c>
       <c r="I102" t="n">
-        <v>155922.9</v>
+        <v>305190.9</v>
       </c>
       <c r="J102" t="n">
-        <v>144737.4</v>
+        <v>274597.4</v>
       </c>
       <c r="K102" t="n">
-        <v>128895.8</v>
+        <v>731026.2</v>
       </c>
       <c r="L102" t="n">
-        <v>195460</v>
+        <v>544562.4</v>
       </c>
       <c r="M102" t="n">
-        <v>10092</v>
+        <v>705227.9</v>
       </c>
       <c r="N102" t="n">
-        <v>174838.2</v>
+        <v>256970.1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>490268.9</v>
+      </c>
+      <c r="P102" t="n">
+        <v>500262.3</v>
       </c>
     </row>
     <row r="103">
@@ -6234,28 +6854,34 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>72094.10000000001</v>
+        <v>11481</v>
       </c>
       <c r="H103" t="n">
-        <v>85245</v>
+        <v>968709.4</v>
       </c>
       <c r="I103" t="n">
-        <v>170261.1</v>
+        <v>795345.5</v>
       </c>
       <c r="J103" t="n">
-        <v>2013.7</v>
+        <v>77483.39999999999</v>
       </c>
       <c r="K103" t="n">
-        <v>129467.9</v>
+        <v>268395.5</v>
       </c>
       <c r="L103" t="n">
-        <v>178914</v>
+        <v>647634.7</v>
       </c>
       <c r="M103" t="n">
-        <v>53720.4</v>
+        <v>811408.9</v>
       </c>
       <c r="N103" t="n">
-        <v>74574.60000000001</v>
+        <v>824689.8</v>
+      </c>
+      <c r="O103" t="n">
+        <v>909700.8</v>
+      </c>
+      <c r="P103" t="n">
+        <v>833354.2</v>
       </c>
     </row>
     <row r="104">
@@ -6290,28 +6916,34 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>5700.5</v>
+        <v>720721.8</v>
       </c>
       <c r="H104" t="n">
-        <v>22832.4</v>
+        <v>579180.3</v>
       </c>
       <c r="I104" t="n">
-        <v>34498.2</v>
+        <v>227595.5</v>
       </c>
       <c r="J104" t="n">
-        <v>21092.8</v>
+        <v>285728.2</v>
       </c>
       <c r="K104" t="n">
-        <v>8347.299999999999</v>
+        <v>851713.2</v>
       </c>
       <c r="L104" t="n">
-        <v>36323.3</v>
+        <v>908411.4</v>
       </c>
       <c r="M104" t="n">
-        <v>42219</v>
+        <v>386078.8</v>
       </c>
       <c r="N104" t="n">
-        <v>45562.2</v>
+        <v>481847.8</v>
+      </c>
+      <c r="O104" t="n">
+        <v>73490.7</v>
+      </c>
+      <c r="P104" t="n">
+        <v>806200.2</v>
       </c>
     </row>
     <row r="105">
@@ -6346,28 +6978,34 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>113823.2</v>
+        <v>681710.4</v>
       </c>
       <c r="H105" t="n">
-        <v>122295.7</v>
+        <v>542195.2</v>
       </c>
       <c r="I105" t="n">
-        <v>122302.8</v>
+        <v>23664.4</v>
       </c>
       <c r="J105" t="n">
-        <v>175999.7</v>
+        <v>271715.1</v>
       </c>
       <c r="K105" t="n">
-        <v>178361.2</v>
+        <v>830731</v>
       </c>
       <c r="L105" t="n">
-        <v>97665.5</v>
+        <v>826631.2</v>
       </c>
       <c r="M105" t="n">
-        <v>88182.3</v>
+        <v>663688.8</v>
       </c>
       <c r="N105" t="n">
-        <v>131022.3</v>
+        <v>806488.5</v>
+      </c>
+      <c r="O105" t="n">
+        <v>80790.5</v>
+      </c>
+      <c r="P105" t="n">
+        <v>72075.5</v>
       </c>
     </row>
     <row r="106">
@@ -6402,28 +7040,34 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>536970.3</v>
       </c>
       <c r="H106" t="n">
-        <v>26245.6</v>
+        <v>747975.6</v>
       </c>
       <c r="I106" t="n">
-        <v>36191.4</v>
+        <v>193129.8</v>
       </c>
       <c r="J106" t="n">
-        <v>47788.5</v>
+        <v>319709.6</v>
       </c>
       <c r="K106" t="n">
-        <v>25959.8</v>
+        <v>86662.89999999999</v>
       </c>
       <c r="L106" t="n">
-        <v>30915.8</v>
+        <v>71409.8</v>
       </c>
       <c r="M106" t="n">
-        <v>36335.3</v>
+        <v>820747.6</v>
       </c>
       <c r="N106" t="n">
-        <v>33188.9</v>
+        <v>746559.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>608297.4</v>
+      </c>
+      <c r="P106" t="n">
+        <v>861764.4</v>
       </c>
     </row>
     <row r="107">
@@ -6458,28 +7102,34 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>7441.2</v>
+        <v>266825.2</v>
       </c>
       <c r="H107" t="n">
-        <v>44604.2</v>
+        <v>57165.3</v>
       </c>
       <c r="I107" t="n">
-        <v>592.1</v>
+        <v>328262</v>
       </c>
       <c r="J107" t="n">
-        <v>25283.3</v>
+        <v>540152.2</v>
       </c>
       <c r="K107" t="n">
-        <v>24796.8</v>
+        <v>881631.2</v>
       </c>
       <c r="L107" t="n">
-        <v>37574</v>
+        <v>165922.8</v>
       </c>
       <c r="M107" t="n">
-        <v>16551.4</v>
+        <v>980818.1</v>
       </c>
       <c r="N107" t="n">
-        <v>25351.4</v>
+        <v>338715.3</v>
+      </c>
+      <c r="O107" t="n">
+        <v>65682.2</v>
+      </c>
+      <c r="P107" t="n">
+        <v>42302.3</v>
       </c>
     </row>
     <row r="108">
@@ -6514,28 +7164,34 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>189380.9</v>
+        <v>640961.8</v>
       </c>
       <c r="H108" t="n">
-        <v>39507.4</v>
+        <v>584177.6</v>
       </c>
       <c r="I108" t="n">
-        <v>286560.2</v>
+        <v>864352.9</v>
       </c>
       <c r="J108" t="n">
-        <v>249278.2</v>
+        <v>138374.1</v>
       </c>
       <c r="K108" t="n">
-        <v>490337.3</v>
+        <v>243863.4</v>
       </c>
       <c r="L108" t="n">
-        <v>8982.799999999999</v>
+        <v>307611.8</v>
       </c>
       <c r="M108" t="n">
-        <v>18012.4</v>
+        <v>495328.6</v>
       </c>
       <c r="N108" t="n">
-        <v>412971.8</v>
+        <v>115169.7</v>
+      </c>
+      <c r="O108" t="n">
+        <v>275016</v>
+      </c>
+      <c r="P108" t="n">
+        <v>18741.5</v>
       </c>
     </row>
     <row r="109">
@@ -6570,28 +7226,34 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>48158.9</v>
+        <v>111552.2</v>
       </c>
       <c r="H109" t="n">
-        <v>44506.6</v>
+        <v>502850.4</v>
       </c>
       <c r="I109" t="n">
-        <v>32733.3</v>
+        <v>966889.1</v>
       </c>
       <c r="J109" t="n">
-        <v>17049.3</v>
+        <v>231261.5</v>
       </c>
       <c r="K109" t="n">
-        <v>40831.3</v>
+        <v>464708.5</v>
       </c>
       <c r="L109" t="n">
-        <v>16605.3</v>
+        <v>748957.7</v>
       </c>
       <c r="M109" t="n">
-        <v>30001.6</v>
+        <v>37019.6</v>
       </c>
       <c r="N109" t="n">
-        <v>18171.1</v>
+        <v>962893.3</v>
+      </c>
+      <c r="O109" t="n">
+        <v>633076.7</v>
+      </c>
+      <c r="P109" t="n">
+        <v>921162.4</v>
       </c>
     </row>
     <row r="110">
@@ -6626,28 +7288,34 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>19559.6</v>
+        <v>434765.3</v>
       </c>
       <c r="H110" t="n">
-        <v>519.2</v>
+        <v>852719.9</v>
       </c>
       <c r="I110" t="n">
-        <v>126761.5</v>
+        <v>279125</v>
       </c>
       <c r="J110" t="n">
-        <v>109574.3</v>
+        <v>693949.8</v>
       </c>
       <c r="K110" t="n">
-        <v>21335.9</v>
+        <v>610331.7</v>
       </c>
       <c r="L110" t="n">
-        <v>98525</v>
+        <v>569207</v>
       </c>
       <c r="M110" t="n">
-        <v>148522.8</v>
+        <v>502291.2</v>
       </c>
       <c r="N110" t="n">
-        <v>50917.5</v>
+        <v>140757</v>
+      </c>
+      <c r="O110" t="n">
+        <v>548356.4</v>
+      </c>
+      <c r="P110" t="n">
+        <v>862110</v>
       </c>
     </row>
     <row r="111">
@@ -6682,28 +7350,34 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>6046.1</v>
+        <v>453723.7</v>
       </c>
       <c r="H111" t="n">
-        <v>10787.3</v>
+        <v>157432.7</v>
       </c>
       <c r="I111" t="n">
-        <v>9537</v>
+        <v>641481.7</v>
       </c>
       <c r="J111" t="n">
-        <v>37859.9</v>
+        <v>706419.1</v>
       </c>
       <c r="K111" t="n">
-        <v>31665.7</v>
+        <v>378989.3</v>
       </c>
       <c r="L111" t="n">
-        <v>6169.7</v>
+        <v>288610.6</v>
       </c>
       <c r="M111" t="n">
-        <v>22874.8</v>
+        <v>590180.4</v>
       </c>
       <c r="N111" t="n">
-        <v>25214.8</v>
+        <v>966500.2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>325185.4</v>
+      </c>
+      <c r="P111" t="n">
+        <v>575759.2</v>
       </c>
     </row>
     <row r="112">
@@ -6738,28 +7412,34 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>226.8</v>
+        <v>953815.9</v>
       </c>
       <c r="H112" t="n">
-        <v>27665.8</v>
+        <v>960778.9</v>
       </c>
       <c r="I112" t="n">
-        <v>29260.2</v>
+        <v>399678.4</v>
       </c>
       <c r="J112" t="n">
-        <v>39056.3</v>
+        <v>64228.9</v>
       </c>
       <c r="K112" t="n">
-        <v>34594</v>
+        <v>28700</v>
       </c>
       <c r="L112" t="n">
-        <v>40764.1</v>
+        <v>124353.7</v>
       </c>
       <c r="M112" t="n">
-        <v>32879.5</v>
+        <v>869700.3</v>
       </c>
       <c r="N112" t="n">
-        <v>16099</v>
+        <v>860140.6</v>
+      </c>
+      <c r="O112" t="n">
+        <v>994627.8</v>
+      </c>
+      <c r="P112" t="n">
+        <v>573399.7</v>
       </c>
     </row>
     <row r="113">
@@ -6794,28 +7474,34 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>418955.4</v>
+        <v>875852.9</v>
       </c>
       <c r="H113" t="n">
-        <v>692669.3</v>
+        <v>80111.5</v>
       </c>
       <c r="I113" t="n">
-        <v>398171.1</v>
+        <v>981149.7</v>
       </c>
       <c r="J113" t="n">
-        <v>294526.5</v>
+        <v>407599.4</v>
       </c>
       <c r="K113" t="n">
-        <v>138610.9</v>
+        <v>850952.8</v>
       </c>
       <c r="L113" t="n">
-        <v>886493.6</v>
+        <v>688678</v>
       </c>
       <c r="M113" t="n">
-        <v>843152.9</v>
+        <v>874190.4</v>
       </c>
       <c r="N113" t="n">
-        <v>314253.8</v>
+        <v>724216.7</v>
+      </c>
+      <c r="O113" t="n">
+        <v>530556.8</v>
+      </c>
+      <c r="P113" t="n">
+        <v>709499</v>
       </c>
     </row>
     <row r="114">
@@ -6850,28 +7536,34 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27683.5</v>
+        <v>263389.1</v>
       </c>
       <c r="H114" t="n">
-        <v>10493.5</v>
+        <v>185825</v>
       </c>
       <c r="I114" t="n">
-        <v>34333.7</v>
+        <v>536215.7</v>
       </c>
       <c r="J114" t="n">
-        <v>6642.3</v>
+        <v>542611.1</v>
       </c>
       <c r="K114" t="n">
-        <v>48759.2</v>
+        <v>181839.9</v>
       </c>
       <c r="L114" t="n">
-        <v>27129.1</v>
+        <v>699733.7</v>
       </c>
       <c r="M114" t="n">
-        <v>35520.5</v>
+        <v>440306.2</v>
       </c>
       <c r="N114" t="n">
-        <v>28118.4</v>
+        <v>979942.2</v>
+      </c>
+      <c r="O114" t="n">
+        <v>453715.4</v>
+      </c>
+      <c r="P114" t="n">
+        <v>417694</v>
       </c>
     </row>
     <row r="115">
@@ -6906,28 +7598,34 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>188539.3</v>
+        <v>500586.1</v>
       </c>
       <c r="H115" t="n">
-        <v>134874.8</v>
+        <v>595035.1</v>
       </c>
       <c r="I115" t="n">
-        <v>106817.8</v>
+        <v>939237.1</v>
       </c>
       <c r="J115" t="n">
-        <v>84523.5</v>
+        <v>415774.2</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>212119.9</v>
       </c>
       <c r="L115" t="n">
-        <v>76223.60000000001</v>
+        <v>942676.2</v>
       </c>
       <c r="M115" t="n">
-        <v>11396.4</v>
+        <v>525951.1</v>
       </c>
       <c r="N115" t="n">
-        <v>157123.6</v>
+        <v>967269.7</v>
+      </c>
+      <c r="O115" t="n">
+        <v>605426.8</v>
+      </c>
+      <c r="P115" t="n">
+        <v>115173.4</v>
       </c>
     </row>
     <row r="116">
@@ -6962,28 +7660,34 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>683548.6</v>
+        <v>178651.9</v>
       </c>
       <c r="H116" t="n">
-        <v>62501.8</v>
+        <v>675212.6</v>
       </c>
       <c r="I116" t="n">
-        <v>204398.9</v>
+        <v>115341.8</v>
       </c>
       <c r="J116" t="n">
-        <v>359003.1</v>
+        <v>206834.4</v>
       </c>
       <c r="K116" t="n">
-        <v>616300.8</v>
+        <v>797832.4</v>
       </c>
       <c r="L116" t="n">
-        <v>562104</v>
+        <v>500472.2</v>
       </c>
       <c r="M116" t="n">
-        <v>647295.9</v>
+        <v>456928.1</v>
       </c>
       <c r="N116" t="n">
-        <v>511166.8</v>
+        <v>804587.6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>99178.5</v>
+      </c>
+      <c r="P116" t="n">
+        <v>20856.6</v>
       </c>
     </row>
     <row r="117">
@@ -7018,28 +7722,34 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>696280.4</v>
+        <v>912627.8</v>
       </c>
       <c r="H117" t="n">
-        <v>47456.4</v>
+        <v>235203.9</v>
       </c>
       <c r="I117" t="n">
-        <v>416858</v>
+        <v>970400.6</v>
       </c>
       <c r="J117" t="n">
-        <v>685306.2</v>
+        <v>420143.5</v>
       </c>
       <c r="K117" t="n">
-        <v>54275.3</v>
+        <v>340338.8</v>
       </c>
       <c r="L117" t="n">
-        <v>203485.7</v>
+        <v>493795.2</v>
       </c>
       <c r="M117" t="n">
-        <v>860514.5</v>
+        <v>722443.8</v>
       </c>
       <c r="N117" t="n">
-        <v>225935.7</v>
+        <v>365775</v>
+      </c>
+      <c r="O117" t="n">
+        <v>701779.4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>324768.2</v>
       </c>
     </row>
     <row r="118">
@@ -7074,28 +7784,34 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>354801.8</v>
+        <v>870518.6</v>
       </c>
       <c r="H118" t="n">
-        <v>294233.8</v>
+        <v>119886.6</v>
       </c>
       <c r="I118" t="n">
-        <v>98314.89999999999</v>
+        <v>178567.8</v>
       </c>
       <c r="J118" t="n">
-        <v>96829.5</v>
+        <v>904838.5</v>
       </c>
       <c r="K118" t="n">
-        <v>491728.3</v>
+        <v>880320</v>
       </c>
       <c r="L118" t="n">
-        <v>481241.4</v>
+        <v>80441.89999999999</v>
       </c>
       <c r="M118" t="n">
-        <v>59765</v>
+        <v>409978.6</v>
       </c>
       <c r="N118" t="n">
-        <v>139628.2</v>
+        <v>790682</v>
+      </c>
+      <c r="O118" t="n">
+        <v>852792.7</v>
+      </c>
+      <c r="P118" t="n">
+        <v>801322.2</v>
       </c>
     </row>
     <row r="119">
@@ -7130,28 +7846,34 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>32252.9</v>
+        <v>298444.8</v>
       </c>
       <c r="H119" t="n">
-        <v>1208.6</v>
+        <v>890287.3</v>
       </c>
       <c r="I119" t="n">
-        <v>187503.9</v>
+        <v>962534.3</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>584079.4</v>
       </c>
       <c r="K119" t="n">
-        <v>119408.3</v>
+        <v>701183.8</v>
       </c>
       <c r="L119" t="n">
-        <v>125103.3</v>
+        <v>39860.8</v>
       </c>
       <c r="M119" t="n">
-        <v>60286.9</v>
+        <v>654781.3</v>
       </c>
       <c r="N119" t="n">
-        <v>110068</v>
+        <v>13918.7</v>
+      </c>
+      <c r="O119" t="n">
+        <v>650916.7</v>
+      </c>
+      <c r="P119" t="n">
+        <v>618125.3</v>
       </c>
     </row>
     <row r="120">
@@ -7186,28 +7908,34 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>141559.7</v>
+        <v>638949.5</v>
       </c>
       <c r="H120" t="n">
-        <v>191401</v>
+        <v>246215.3</v>
       </c>
       <c r="I120" t="n">
-        <v>157268.7</v>
+        <v>265466.4</v>
       </c>
       <c r="J120" t="n">
-        <v>108652.6</v>
+        <v>695523</v>
       </c>
       <c r="K120" t="n">
-        <v>69932.60000000001</v>
+        <v>276268.6</v>
       </c>
       <c r="L120" t="n">
-        <v>132693.8</v>
+        <v>432028.7</v>
       </c>
       <c r="M120" t="n">
-        <v>58771.4</v>
+        <v>154361.2</v>
       </c>
       <c r="N120" t="n">
-        <v>123686.7</v>
+        <v>536572.3</v>
+      </c>
+      <c r="O120" t="n">
+        <v>768962.7</v>
+      </c>
+      <c r="P120" t="n">
+        <v>832025.9</v>
       </c>
     </row>
     <row r="121">
@@ -7242,28 +7970,34 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>28071.1</v>
+        <v>608970.2</v>
       </c>
       <c r="H121" t="n">
-        <v>32468.5</v>
+        <v>594519.2</v>
       </c>
       <c r="I121" t="n">
-        <v>17306.9</v>
+        <v>108402.5</v>
       </c>
       <c r="J121" t="n">
-        <v>32116.8</v>
+        <v>856732</v>
       </c>
       <c r="K121" t="n">
-        <v>12198.9</v>
+        <v>10151.1</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>322321.6</v>
       </c>
       <c r="M121" t="n">
-        <v>19074.8</v>
+        <v>469490.6</v>
       </c>
       <c r="N121" t="n">
-        <v>5677.6</v>
+        <v>454786</v>
+      </c>
+      <c r="O121" t="n">
+        <v>720839.9</v>
+      </c>
+      <c r="P121" t="n">
+        <v>919769.8</v>
       </c>
     </row>
     <row r="122">
@@ -7298,28 +8032,34 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>362015.4</v>
+        <v>152839.3</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>619381.5</v>
       </c>
       <c r="I122" t="n">
-        <v>385270.1</v>
+        <v>434563.8</v>
       </c>
       <c r="J122" t="n">
-        <v>254416.9</v>
+        <v>765594.6</v>
       </c>
       <c r="K122" t="n">
-        <v>148287.3</v>
+        <v>948062.6</v>
       </c>
       <c r="L122" t="n">
-        <v>160224.3</v>
+        <v>250367.9</v>
       </c>
       <c r="M122" t="n">
-        <v>48068.6</v>
+        <v>969203.6</v>
       </c>
       <c r="N122" t="n">
-        <v>386681.9</v>
+        <v>672828.4</v>
+      </c>
+      <c r="O122" t="n">
+        <v>215023.1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>88129.89999999999</v>
       </c>
     </row>
   </sheetData>
